--- a/calculator/templates/Calculation-template-Mal.xlsx
+++ b/calculator/templates/Calculation-template-Mal.xlsx
@@ -953,53 +953,43 @@
         <v>0</v>
       </c>
       <c r="S7" s="12">
-        <f t="shared" ref="S7" si="0">+Q7*R7</f>
-        <v>0</v>
+        <f>ROUND(Q7*R7,2)</f>
       </c>
       <c r="T7" s="5">
         <v>0</v>
       </c>
       <c r="U7" s="12">
-        <f>S7*(1-T7)</f>
-        <v>0</v>
+        <f>ROUND(S7*(1-T7),2)</f>
       </c>
       <c r="V7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W7" s="11">
         <f>IFERROR(VLOOKUP(V7,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X7" s="12">
-        <f t="shared" ref="X7" si="1">U7*W7</f>
-        <v>0</v>
+        <f>ROUND(U7*W7,2)</f>
       </c>
       <c r="Y7" s="26">
         <f>Q7</f>
-        <v>0</v>
       </c>
       <c r="Z7" s="12">
-        <f t="shared" ref="Z7" si="2">+Y7*R7</f>
-        <v>0</v>
+        <f>ROUND(Y7*R7,2)</f>
       </c>
       <c r="AA7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB7" s="11">
         <f>IFERROR(VLOOKUP(AA7,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC7" s="12">
-        <f t="shared" ref="AC7" si="3">+Y7*AB7*R7</f>
-        <v>0</v>
+        <f>ROUND(Y7*AB7*R7,2)</f>
       </c>
       <c r="AD7" s="12">
-        <f t="shared" ref="AD7" si="4">+AC7-X7</f>
-        <v>0</v>
+        <f>ROUND(AC7-X7,2)</f>
       </c>
       <c r="AE7" s="13">
-        <f t="shared" ref="AE7" si="5">IFERROR(AD7/AC7,0)</f>
-        <v>0</v>
+        <f>IFERROR(AD7/AC7,0)</f>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.25">
@@ -1021,53 +1011,43 @@
         <v>0</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" ref="S8:S11" si="6">+Q8*R8</f>
-        <v>0</v>
+        <f>ROUND(Q8*R8,2)</f>
       </c>
       <c r="T8" s="5">
         <v>0</v>
       </c>
       <c r="U8" s="12">
-        <f t="shared" ref="U8:U11" si="7">S8*(1-T8)</f>
-        <v>0</v>
+        <f>ROUND(S8*(1-T8),2)</f>
       </c>
       <c r="V8" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W8" s="11">
         <f>IFERROR(VLOOKUP(V8,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X8" s="12">
-        <f t="shared" ref="X8:X11" si="8">U8*W8</f>
-        <v>0</v>
+        <f>ROUND(U8*W8,2)</f>
       </c>
       <c r="Y8" s="26">
-        <f t="shared" ref="Y8:Y11" si="9">Q8</f>
-        <v>0</v>
+        <f>Q8</f>
       </c>
       <c r="Z8" s="12">
-        <f t="shared" ref="Z8:Z11" si="10">+Y8*R8</f>
-        <v>0</v>
+        <f>ROUND(Y8*R8,2)</f>
       </c>
       <c r="AA8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB8" s="11">
         <f>IFERROR(VLOOKUP(AA8,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC8" s="12">
-        <f t="shared" ref="AC8:AC11" si="11">+Y8*AB8*R8</f>
-        <v>0</v>
+        <f>ROUND(Y8*AB8*R8,2)</f>
       </c>
       <c r="AD8" s="12">
-        <f t="shared" ref="AD8:AD11" si="12">+AC8-X8</f>
-        <v>0</v>
+        <f>ROUND(AC8-X8,2)</f>
       </c>
       <c r="AE8" s="13">
-        <f t="shared" ref="AE8:AE11" si="13">IFERROR(AD8/AC8,0)</f>
-        <v>0</v>
+        <f>IFERROR(AD8/AC8,0)</f>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.25">
@@ -1089,53 +1069,43 @@
         <v>0</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>ROUND(Q9*R9,2)</f>
       </c>
       <c r="T9" s="5">
         <v>0</v>
       </c>
       <c r="U9" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>ROUND(S9*(1-T9),2)</f>
       </c>
       <c r="V9" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W9" s="11">
         <f>IFERROR(VLOOKUP(V9,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X9" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>ROUND(U9*W9,2)</f>
       </c>
       <c r="Y9" s="26">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>Q9</f>
       </c>
       <c r="Z9" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>ROUND(Y9*R9,2)</f>
       </c>
       <c r="AA9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB9" s="11">
         <f>IFERROR(VLOOKUP(AA9,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC9" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>ROUND(Y9*AB9*R9,2)</f>
       </c>
       <c r="AD9" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>ROUND(AC9-X9,2)</f>
       </c>
       <c r="AE9" s="13">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>IFERROR(AD9/AC9,0)</f>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.25">
@@ -1157,53 +1127,43 @@
         <v>0</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>ROUND(Q10*R10,2)</f>
       </c>
       <c r="T10" s="5">
         <v>0</v>
       </c>
       <c r="U10" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>ROUND(S10*(1-T10),2)</f>
       </c>
       <c r="V10" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W10" s="11">
         <f>IFERROR(VLOOKUP(V10,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X10" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>ROUND(U10*W10,2)</f>
       </c>
       <c r="Y10" s="26">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>Q10</f>
       </c>
       <c r="Z10" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>ROUND(Y10*R10,2)</f>
       </c>
       <c r="AA10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB10" s="11">
         <f>IFERROR(VLOOKUP(AA10,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC10" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>ROUND(Y10*AB10*R10,2)</f>
       </c>
       <c r="AD10" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>ROUND(AC10-X10,2)</f>
       </c>
       <c r="AE10" s="13">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>IFERROR(AD10/AC10,0)</f>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.25">
@@ -1225,53 +1185,43 @@
         <v>0</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>ROUND(Q11*R11,2)</f>
       </c>
       <c r="T11" s="5">
         <v>0</v>
       </c>
       <c r="U11" s="12">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>ROUND(S11*(1-T11),2)</f>
       </c>
       <c r="V11" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W11" s="11">
         <f>IFERROR(VLOOKUP(V11,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X11" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>ROUND(U11*W11,2)</f>
       </c>
       <c r="Y11" s="26">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>Q11</f>
       </c>
       <c r="Z11" s="12">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>ROUND(Y11*R11,2)</f>
       </c>
       <c r="AA11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB11" s="11">
         <f>IFERROR(VLOOKUP(AA11,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC11" s="12">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>ROUND(Y11*AB11*R11,2)</f>
       </c>
       <c r="AD11" s="12">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>ROUND(AC11-X11,2)</f>
       </c>
       <c r="AE11" s="13">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>IFERROR(AD11/AC11,0)</f>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.25">
@@ -1293,53 +1243,43 @@
         <v>0</v>
       </c>
       <c r="S12" s="12">
-        <f t="shared" ref="S12:S99" si="14">+Q12*R12</f>
-        <v>0</v>
+        <f>ROUND(Q12*R12,2)</f>
       </c>
       <c r="T12" s="5">
         <v>0</v>
       </c>
       <c r="U12" s="12">
-        <f t="shared" ref="U12:U99" si="15">S12*(1-T12)</f>
-        <v>0</v>
+        <f>ROUND(S12*(1-T12),2)</f>
       </c>
       <c r="V12" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W12" s="11">
         <f>IFERROR(VLOOKUP(V12,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X12" s="12">
-        <f t="shared" ref="X12:X99" si="16">U12*W12</f>
-        <v>0</v>
+        <f>ROUND(U12*W12,2)</f>
       </c>
       <c r="Y12" s="26">
-        <f t="shared" ref="Y12:Y99" si="17">Q12</f>
-        <v>0</v>
+        <f>Q12</f>
       </c>
       <c r="Z12" s="12">
-        <f t="shared" ref="Z12:Z99" si="18">+Y12*R12</f>
-        <v>0</v>
+        <f>ROUND(Y12*R12,2)</f>
       </c>
       <c r="AA12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB12" s="11">
         <f>IFERROR(VLOOKUP(AA12,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC12" s="12">
-        <f t="shared" ref="AC12:AC99" si="19">+Y12*AB12*R12</f>
-        <v>0</v>
+        <f>ROUND(Y12*AB12*R12,2)</f>
       </c>
       <c r="AD12" s="12">
-        <f t="shared" ref="AD12:AD99" si="20">+AC12-X12</f>
-        <v>0</v>
+        <f>ROUND(AC12-X12,2)</f>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" ref="AE12:AE99" si="21">IFERROR(AD12/AC12,0)</f>
-        <v>0</v>
+        <f>IFERROR(AD12/AC12,0)</f>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.25">
@@ -1361,53 +1301,43 @@
         <v>0</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q13*R13,2)</f>
       </c>
       <c r="T13" s="5">
         <v>0</v>
       </c>
       <c r="U13" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S13*(1-T13),2)</f>
       </c>
       <c r="V13" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W13" s="11">
         <f>IFERROR(VLOOKUP(V13,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X13" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U13*W13,2)</f>
       </c>
       <c r="Y13" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q13</f>
       </c>
       <c r="Z13" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y13*R13,2)</f>
       </c>
       <c r="AA13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB13" s="11">
         <f>IFERROR(VLOOKUP(AA13,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC13" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y13*AB13*R13,2)</f>
       </c>
       <c r="AD13" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC13-X13,2)</f>
       </c>
       <c r="AE13" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD13/AC13,0)</f>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.25">
@@ -1429,53 +1359,43 @@
         <v>0</v>
       </c>
       <c r="S14" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q14*R14,2)</f>
       </c>
       <c r="T14" s="5">
         <v>0</v>
       </c>
       <c r="U14" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S14*(1-T14),2)</f>
       </c>
       <c r="V14" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W14" s="11">
         <f>IFERROR(VLOOKUP(V14,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X14" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U14*W14,2)</f>
       </c>
       <c r="Y14" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q14</f>
       </c>
       <c r="Z14" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y14*R14,2)</f>
       </c>
       <c r="AA14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB14" s="11">
         <f>IFERROR(VLOOKUP(AA14,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC14" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y14*AB14*R14,2)</f>
       </c>
       <c r="AD14" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC14-X14,2)</f>
       </c>
       <c r="AE14" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD14/AC14,0)</f>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.25">
@@ -1497,53 +1417,43 @@
         <v>0</v>
       </c>
       <c r="S15" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q15*R15,2)</f>
       </c>
       <c r="T15" s="5">
         <v>0</v>
       </c>
       <c r="U15" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S15*(1-T15),2)</f>
       </c>
       <c r="V15" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W15" s="11">
         <f>IFERROR(VLOOKUP(V15,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X15" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U15*W15,2)</f>
       </c>
       <c r="Y15" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q15</f>
       </c>
       <c r="Z15" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y15*R15,2)</f>
       </c>
       <c r="AA15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB15" s="11">
         <f>IFERROR(VLOOKUP(AA15,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC15" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y15*AB15*R15,2)</f>
       </c>
       <c r="AD15" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC15-X15,2)</f>
       </c>
       <c r="AE15" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD15/AC15,0)</f>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.25">
@@ -1565,53 +1475,43 @@
         <v>0</v>
       </c>
       <c r="S16" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q16*R16,2)</f>
       </c>
       <c r="T16" s="5">
         <v>0</v>
       </c>
       <c r="U16" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S16*(1-T16),2)</f>
       </c>
       <c r="V16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W16" s="11">
         <f>IFERROR(VLOOKUP(V16,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X16" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U16*W16,2)</f>
       </c>
       <c r="Y16" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q16</f>
       </c>
       <c r="Z16" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y16*R16,2)</f>
       </c>
       <c r="AA16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB16" s="11">
         <f>IFERROR(VLOOKUP(AA16,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC16" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y16*AB16*R16,2)</f>
       </c>
       <c r="AD16" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC16-X16,2)</f>
       </c>
       <c r="AE16" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD16/AC16,0)</f>
       </c>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.25">
@@ -1633,53 +1533,43 @@
         <v>0</v>
       </c>
       <c r="S17" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q17*R17,2)</f>
       </c>
       <c r="T17" s="5">
         <v>0</v>
       </c>
       <c r="U17" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S17*(1-T17),2)</f>
       </c>
       <c r="V17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W17" s="11">
         <f>IFERROR(VLOOKUP(V17,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X17" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U17*W17,2)</f>
       </c>
       <c r="Y17" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q17</f>
       </c>
       <c r="Z17" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y17*R17,2)</f>
       </c>
       <c r="AA17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB17" s="11">
         <f>IFERROR(VLOOKUP(AA17,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC17" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y17*AB17*R17,2)</f>
       </c>
       <c r="AD17" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC17-X17,2)</f>
       </c>
       <c r="AE17" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD17/AC17,0)</f>
       </c>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.25">
@@ -1701,53 +1591,43 @@
         <v>0</v>
       </c>
       <c r="S18" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q18*R18,2)</f>
       </c>
       <c r="T18" s="5">
         <v>0</v>
       </c>
       <c r="U18" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S18*(1-T18),2)</f>
       </c>
       <c r="V18" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W18" s="11">
         <f>IFERROR(VLOOKUP(V18,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X18" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U18*W18,2)</f>
       </c>
       <c r="Y18" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q18</f>
       </c>
       <c r="Z18" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y18*R18,2)</f>
       </c>
       <c r="AA18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB18" s="11">
         <f>IFERROR(VLOOKUP(AA18,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC18" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y18*AB18*R18,2)</f>
       </c>
       <c r="AD18" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC18-X18,2)</f>
       </c>
       <c r="AE18" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD18/AC18,0)</f>
       </c>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
@@ -1769,53 +1649,43 @@
         <v>0</v>
       </c>
       <c r="S19" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q19*R19,2)</f>
       </c>
       <c r="T19" s="5">
         <v>0</v>
       </c>
       <c r="U19" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S19*(1-T19),2)</f>
       </c>
       <c r="V19" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W19" s="11">
         <f>IFERROR(VLOOKUP(V19,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X19" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U19*W19,2)</f>
       </c>
       <c r="Y19" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q19</f>
       </c>
       <c r="Z19" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y19*R19,2)</f>
       </c>
       <c r="AA19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB19" s="11">
         <f>IFERROR(VLOOKUP(AA19,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC19" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y19*AB19*R19,2)</f>
       </c>
       <c r="AD19" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC19-X19,2)</f>
       </c>
       <c r="AE19" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD19/AC19,0)</f>
       </c>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
@@ -1837,53 +1707,43 @@
         <v>0</v>
       </c>
       <c r="S20" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q20*R20,2)</f>
       </c>
       <c r="T20" s="5">
         <v>0</v>
       </c>
       <c r="U20" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S20*(1-T20),2)</f>
       </c>
       <c r="V20" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W20" s="11">
         <f>IFERROR(VLOOKUP(V20,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X20" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U20*W20,2)</f>
       </c>
       <c r="Y20" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q20</f>
       </c>
       <c r="Z20" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y20*R20,2)</f>
       </c>
       <c r="AA20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB20" s="11">
         <f>IFERROR(VLOOKUP(AA20,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC20" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y20*AB20*R20,2)</f>
       </c>
       <c r="AD20" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC20-X20,2)</f>
       </c>
       <c r="AE20" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD20/AC20,0)</f>
       </c>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.25">
@@ -1905,53 +1765,43 @@
         <v>0</v>
       </c>
       <c r="S21" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q21*R21,2)</f>
       </c>
       <c r="T21" s="5">
         <v>0</v>
       </c>
       <c r="U21" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S21*(1-T21),2)</f>
       </c>
       <c r="V21" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W21" s="11">
         <f>IFERROR(VLOOKUP(V21,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X21" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U21*W21,2)</f>
       </c>
       <c r="Y21" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q21</f>
       </c>
       <c r="Z21" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y21*R21,2)</f>
       </c>
       <c r="AA21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB21" s="11">
         <f>IFERROR(VLOOKUP(AA21,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC21" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y21*AB21*R21,2)</f>
       </c>
       <c r="AD21" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC21-X21,2)</f>
       </c>
       <c r="AE21" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD21/AC21,0)</f>
       </c>
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.25">
@@ -1973,53 +1823,43 @@
         <v>0</v>
       </c>
       <c r="S22" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q22*R22,2)</f>
       </c>
       <c r="T22" s="5">
         <v>0</v>
       </c>
       <c r="U22" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S22*(1-T22),2)</f>
       </c>
       <c r="V22" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W22" s="11">
         <f>IFERROR(VLOOKUP(V22,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X22" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U22*W22,2)</f>
       </c>
       <c r="Y22" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q22</f>
       </c>
       <c r="Z22" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y22*R22,2)</f>
       </c>
       <c r="AA22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB22" s="11">
         <f>IFERROR(VLOOKUP(AA22,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC22" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y22*AB22*R22,2)</f>
       </c>
       <c r="AD22" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC22-X22,2)</f>
       </c>
       <c r="AE22" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD22/AC22,0)</f>
       </c>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.25">
@@ -2041,53 +1881,43 @@
         <v>0</v>
       </c>
       <c r="S23" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q23*R23,2)</f>
       </c>
       <c r="T23" s="5">
         <v>0</v>
       </c>
       <c r="U23" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S23*(1-T23),2)</f>
       </c>
       <c r="V23" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W23" s="11">
         <f>IFERROR(VLOOKUP(V23,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X23" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U23*W23,2)</f>
       </c>
       <c r="Y23" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q23</f>
       </c>
       <c r="Z23" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y23*R23,2)</f>
       </c>
       <c r="AA23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB23" s="11">
         <f>IFERROR(VLOOKUP(AA23,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC23" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y23*AB23*R23,2)</f>
       </c>
       <c r="AD23" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC23-X23,2)</f>
       </c>
       <c r="AE23" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD23/AC23,0)</f>
       </c>
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.25">
@@ -2109,53 +1939,43 @@
         <v>0</v>
       </c>
       <c r="S24" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q24*R24,2)</f>
       </c>
       <c r="T24" s="5">
         <v>0</v>
       </c>
       <c r="U24" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S24*(1-T24),2)</f>
       </c>
       <c r="V24" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W24" s="11">
         <f>IFERROR(VLOOKUP(V24,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X24" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U24*W24,2)</f>
       </c>
       <c r="Y24" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q24</f>
       </c>
       <c r="Z24" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y24*R24,2)</f>
       </c>
       <c r="AA24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB24" s="11">
         <f>IFERROR(VLOOKUP(AA24,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC24" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y24*AB24*R24,2)</f>
       </c>
       <c r="AD24" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC24-X24,2)</f>
       </c>
       <c r="AE24" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD24/AC24,0)</f>
       </c>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.25">
@@ -2177,53 +1997,43 @@
         <v>0</v>
       </c>
       <c r="S25" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q25*R25,2)</f>
       </c>
       <c r="T25" s="5">
         <v>0</v>
       </c>
       <c r="U25" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S25*(1-T25),2)</f>
       </c>
       <c r="V25" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W25" s="11">
         <f>IFERROR(VLOOKUP(V25,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X25" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U25*W25,2)</f>
       </c>
       <c r="Y25" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q25</f>
       </c>
       <c r="Z25" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y25*R25,2)</f>
       </c>
       <c r="AA25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB25" s="11">
         <f>IFERROR(VLOOKUP(AA25,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC25" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y25*AB25*R25,2)</f>
       </c>
       <c r="AD25" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC25-X25,2)</f>
       </c>
       <c r="AE25" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD25/AC25,0)</f>
       </c>
     </row>
     <row r="26" spans="2:31" x14ac:dyDescent="0.25">
@@ -2245,53 +2055,43 @@
         <v>0</v>
       </c>
       <c r="S26" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q26*R26,2)</f>
       </c>
       <c r="T26" s="5">
         <v>0</v>
       </c>
       <c r="U26" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S26*(1-T26),2)</f>
       </c>
       <c r="V26" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W26" s="11">
         <f>IFERROR(VLOOKUP(V26,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X26" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U26*W26,2)</f>
       </c>
       <c r="Y26" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q26</f>
       </c>
       <c r="Z26" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y26*R26,2)</f>
       </c>
       <c r="AA26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB26" s="11">
         <f>IFERROR(VLOOKUP(AA26,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC26" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y26*AB26*R26,2)</f>
       </c>
       <c r="AD26" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC26-X26,2)</f>
       </c>
       <c r="AE26" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD26/AC26,0)</f>
       </c>
     </row>
     <row r="27" spans="2:31" x14ac:dyDescent="0.25">
@@ -2313,53 +2113,43 @@
         <v>0</v>
       </c>
       <c r="S27" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q27*R27,2)</f>
       </c>
       <c r="T27" s="5">
         <v>0</v>
       </c>
       <c r="U27" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S27*(1-T27),2)</f>
       </c>
       <c r="V27" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W27" s="11">
         <f>IFERROR(VLOOKUP(V27,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U27*W27,2)</f>
       </c>
       <c r="Y27" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q27</f>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y27*R27,2)</f>
       </c>
       <c r="AA27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB27" s="11">
         <f>IFERROR(VLOOKUP(AA27,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC27" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y27*AB27*R27,2)</f>
       </c>
       <c r="AD27" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC27-X27,2)</f>
       </c>
       <c r="AE27" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD27/AC27,0)</f>
       </c>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.25">
@@ -2381,53 +2171,43 @@
         <v>0</v>
       </c>
       <c r="S28" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q28*R28,2)</f>
       </c>
       <c r="T28" s="5">
         <v>0</v>
       </c>
       <c r="U28" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S28*(1-T28),2)</f>
       </c>
       <c r="V28" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W28" s="11">
         <f>IFERROR(VLOOKUP(V28,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U28*W28,2)</f>
       </c>
       <c r="Y28" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q28</f>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y28*R28,2)</f>
       </c>
       <c r="AA28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB28" s="11">
         <f>IFERROR(VLOOKUP(AA28,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC28" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y28*AB28*R28,2)</f>
       </c>
       <c r="AD28" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC28-X28,2)</f>
       </c>
       <c r="AE28" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD28/AC28,0)</f>
       </c>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.25">
@@ -2449,53 +2229,43 @@
         <v>0</v>
       </c>
       <c r="S29" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q29*R29,2)</f>
       </c>
       <c r="T29" s="5">
         <v>0</v>
       </c>
       <c r="U29" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S29*(1-T29),2)</f>
       </c>
       <c r="V29" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W29" s="11">
         <f>IFERROR(VLOOKUP(V29,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X29" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U29*W29,2)</f>
       </c>
       <c r="Y29" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q29</f>
       </c>
       <c r="Z29" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y29*R29,2)</f>
       </c>
       <c r="AA29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB29" s="11">
         <f>IFERROR(VLOOKUP(AA29,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC29" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y29*AB29*R29,2)</f>
       </c>
       <c r="AD29" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC29-X29,2)</f>
       </c>
       <c r="AE29" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD29/AC29,0)</f>
       </c>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.25">
@@ -2517,53 +2287,43 @@
         <v>0</v>
       </c>
       <c r="S30" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q30*R30,2)</f>
       </c>
       <c r="T30" s="5">
         <v>0</v>
       </c>
       <c r="U30" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S30*(1-T30),2)</f>
       </c>
       <c r="V30" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W30" s="11">
         <f>IFERROR(VLOOKUP(V30,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X30" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U30*W30,2)</f>
       </c>
       <c r="Y30" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q30</f>
       </c>
       <c r="Z30" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y30*R30,2)</f>
       </c>
       <c r="AA30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB30" s="11">
         <f>IFERROR(VLOOKUP(AA30,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC30" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y30*AB30*R30,2)</f>
       </c>
       <c r="AD30" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC30-X30,2)</f>
       </c>
       <c r="AE30" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD30/AC30,0)</f>
       </c>
     </row>
     <row r="31" spans="2:31" x14ac:dyDescent="0.25">
@@ -2585,53 +2345,43 @@
         <v>0</v>
       </c>
       <c r="S31" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q31*R31,2)</f>
       </c>
       <c r="T31" s="5">
         <v>0</v>
       </c>
       <c r="U31" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S31*(1-T31),2)</f>
       </c>
       <c r="V31" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W31" s="11">
         <f>IFERROR(VLOOKUP(V31,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X31" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U31*W31,2)</f>
       </c>
       <c r="Y31" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q31</f>
       </c>
       <c r="Z31" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y31*R31,2)</f>
       </c>
       <c r="AA31" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB31" s="11">
         <f>IFERROR(VLOOKUP(AA31,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC31" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y31*AB31*R31,2)</f>
       </c>
       <c r="AD31" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC31-X31,2)</f>
       </c>
       <c r="AE31" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD31/AC31,0)</f>
       </c>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.25">
@@ -2653,53 +2403,43 @@
         <v>0</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q32*R32,2)</f>
       </c>
       <c r="T32" s="5">
         <v>0</v>
       </c>
       <c r="U32" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S32*(1-T32),2)</f>
       </c>
       <c r="V32" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W32" s="11">
         <f>IFERROR(VLOOKUP(V32,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X32" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U32*W32,2)</f>
       </c>
       <c r="Y32" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q32</f>
       </c>
       <c r="Z32" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y32*R32,2)</f>
       </c>
       <c r="AA32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB32" s="11">
         <f>IFERROR(VLOOKUP(AA32,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC32" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y32*AB32*R32,2)</f>
       </c>
       <c r="AD32" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC32-X32,2)</f>
       </c>
       <c r="AE32" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD32/AC32,0)</f>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.25">
@@ -2721,53 +2461,43 @@
         <v>0</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q33*R33,2)</f>
       </c>
       <c r="T33" s="5">
         <v>0</v>
       </c>
       <c r="U33" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S33*(1-T33),2)</f>
       </c>
       <c r="V33" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W33" s="11">
         <f>IFERROR(VLOOKUP(V33,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X33" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U33*W33,2)</f>
       </c>
       <c r="Y33" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q33</f>
       </c>
       <c r="Z33" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y33*R33,2)</f>
       </c>
       <c r="AA33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB33" s="11">
         <f>IFERROR(VLOOKUP(AA33,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC33" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y33*AB33*R33,2)</f>
       </c>
       <c r="AD33" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC33-X33,2)</f>
       </c>
       <c r="AE33" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD33/AC33,0)</f>
       </c>
     </row>
     <row r="34" spans="2:31" x14ac:dyDescent="0.25">
@@ -2789,53 +2519,43 @@
         <v>0</v>
       </c>
       <c r="S34" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q34*R34,2)</f>
       </c>
       <c r="T34" s="5">
         <v>0</v>
       </c>
       <c r="U34" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S34*(1-T34),2)</f>
       </c>
       <c r="V34" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W34" s="11">
         <f>IFERROR(VLOOKUP(V34,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X34" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U34*W34,2)</f>
       </c>
       <c r="Y34" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q34</f>
       </c>
       <c r="Z34" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y34*R34,2)</f>
       </c>
       <c r="AA34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB34" s="11">
         <f>IFERROR(VLOOKUP(AA34,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC34" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y34*AB34*R34,2)</f>
       </c>
       <c r="AD34" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC34-X34,2)</f>
       </c>
       <c r="AE34" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD34/AC34,0)</f>
       </c>
     </row>
     <row r="35" spans="2:31" x14ac:dyDescent="0.25">
@@ -2857,53 +2577,43 @@
         <v>0</v>
       </c>
       <c r="S35" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q35*R35,2)</f>
       </c>
       <c r="T35" s="5">
         <v>0</v>
       </c>
       <c r="U35" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S35*(1-T35),2)</f>
       </c>
       <c r="V35" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W35" s="11">
         <f>IFERROR(VLOOKUP(V35,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X35" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U35*W35,2)</f>
       </c>
       <c r="Y35" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q35</f>
       </c>
       <c r="Z35" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y35*R35,2)</f>
       </c>
       <c r="AA35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB35" s="11">
         <f>IFERROR(VLOOKUP(AA35,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC35" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y35*AB35*R35,2)</f>
       </c>
       <c r="AD35" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC35-X35,2)</f>
       </c>
       <c r="AE35" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD35/AC35,0)</f>
       </c>
     </row>
     <row r="36" spans="2:31" x14ac:dyDescent="0.25">
@@ -2925,53 +2635,43 @@
         <v>0</v>
       </c>
       <c r="S36" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q36*R36,2)</f>
       </c>
       <c r="T36" s="5">
         <v>0</v>
       </c>
       <c r="U36" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S36*(1-T36),2)</f>
       </c>
       <c r="V36" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W36" s="11">
         <f>IFERROR(VLOOKUP(V36,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X36" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U36*W36,2)</f>
       </c>
       <c r="Y36" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q36</f>
       </c>
       <c r="Z36" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y36*R36,2)</f>
       </c>
       <c r="AA36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB36" s="11">
         <f>IFERROR(VLOOKUP(AA36,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC36" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y36*AB36*R36,2)</f>
       </c>
       <c r="AD36" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC36-X36,2)</f>
       </c>
       <c r="AE36" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD36/AC36,0)</f>
       </c>
     </row>
     <row r="37" spans="2:31" x14ac:dyDescent="0.25">
@@ -2993,53 +2693,43 @@
         <v>0</v>
       </c>
       <c r="S37" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q37*R37,2)</f>
       </c>
       <c r="T37" s="5">
         <v>0</v>
       </c>
       <c r="U37" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S37*(1-T37),2)</f>
       </c>
       <c r="V37" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W37" s="11">
         <f>IFERROR(VLOOKUP(V37,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X37" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U37*W37,2)</f>
       </c>
       <c r="Y37" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q37</f>
       </c>
       <c r="Z37" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y37*R37,2)</f>
       </c>
       <c r="AA37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB37" s="11">
         <f>IFERROR(VLOOKUP(AA37,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC37" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y37*AB37*R37,2)</f>
       </c>
       <c r="AD37" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC37-X37,2)</f>
       </c>
       <c r="AE37" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD37/AC37,0)</f>
       </c>
     </row>
     <row r="38" spans="2:31" x14ac:dyDescent="0.25">
@@ -3061,53 +2751,43 @@
         <v>0</v>
       </c>
       <c r="S38" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q38*R38,2)</f>
       </c>
       <c r="T38" s="5">
         <v>0</v>
       </c>
       <c r="U38" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S38*(1-T38),2)</f>
       </c>
       <c r="V38" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W38" s="11">
         <f>IFERROR(VLOOKUP(V38,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X38" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U38*W38,2)</f>
       </c>
       <c r="Y38" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q38</f>
       </c>
       <c r="Z38" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y38*R38,2)</f>
       </c>
       <c r="AA38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB38" s="11">
         <f>IFERROR(VLOOKUP(AA38,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC38" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y38*AB38*R38,2)</f>
       </c>
       <c r="AD38" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC38-X38,2)</f>
       </c>
       <c r="AE38" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD38/AC38,0)</f>
       </c>
     </row>
     <row r="39" spans="2:31" x14ac:dyDescent="0.25">
@@ -3129,53 +2809,43 @@
         <v>0</v>
       </c>
       <c r="S39" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q39*R39,2)</f>
       </c>
       <c r="T39" s="5">
         <v>0</v>
       </c>
       <c r="U39" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S39*(1-T39),2)</f>
       </c>
       <c r="V39" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W39" s="11">
         <f>IFERROR(VLOOKUP(V39,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X39" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U39*W39,2)</f>
       </c>
       <c r="Y39" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q39</f>
       </c>
       <c r="Z39" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y39*R39,2)</f>
       </c>
       <c r="AA39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB39" s="11">
         <f>IFERROR(VLOOKUP(AA39,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC39" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y39*AB39*R39,2)</f>
       </c>
       <c r="AD39" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC39-X39,2)</f>
       </c>
       <c r="AE39" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD39/AC39,0)</f>
       </c>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.25">
@@ -3197,53 +2867,43 @@
         <v>0</v>
       </c>
       <c r="S40" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q40*R40,2)</f>
       </c>
       <c r="T40" s="5">
         <v>0</v>
       </c>
       <c r="U40" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S40*(1-T40),2)</f>
       </c>
       <c r="V40" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W40" s="11">
         <f>IFERROR(VLOOKUP(V40,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X40" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U40*W40,2)</f>
       </c>
       <c r="Y40" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q40</f>
       </c>
       <c r="Z40" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y40*R40,2)</f>
       </c>
       <c r="AA40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB40" s="11">
         <f>IFERROR(VLOOKUP(AA40,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC40" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y40*AB40*R40,2)</f>
       </c>
       <c r="AD40" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC40-X40,2)</f>
       </c>
       <c r="AE40" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD40/AC40,0)</f>
       </c>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.25">
@@ -3265,53 +2925,43 @@
         <v>0</v>
       </c>
       <c r="S41" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q41*R41,2)</f>
       </c>
       <c r="T41" s="5">
         <v>0</v>
       </c>
       <c r="U41" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S41*(1-T41),2)</f>
       </c>
       <c r="V41" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W41" s="11">
         <f>IFERROR(VLOOKUP(V41,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X41" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U41*W41,2)</f>
       </c>
       <c r="Y41" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q41</f>
       </c>
       <c r="Z41" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y41*R41,2)</f>
       </c>
       <c r="AA41" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB41" s="11">
         <f>IFERROR(VLOOKUP(AA41,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC41" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y41*AB41*R41,2)</f>
       </c>
       <c r="AD41" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC41-X41,2)</f>
       </c>
       <c r="AE41" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD41/AC41,0)</f>
       </c>
     </row>
     <row r="42" spans="2:31" x14ac:dyDescent="0.25">
@@ -3333,53 +2983,43 @@
         <v>0</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q42*R42,2)</f>
       </c>
       <c r="T42" s="5">
         <v>0</v>
       </c>
       <c r="U42" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S42*(1-T42),2)</f>
       </c>
       <c r="V42" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W42" s="11">
         <f>IFERROR(VLOOKUP(V42,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X42" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U42*W42,2)</f>
       </c>
       <c r="Y42" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q42</f>
       </c>
       <c r="Z42" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y42*R42,2)</f>
       </c>
       <c r="AA42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB42" s="11">
         <f>IFERROR(VLOOKUP(AA42,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC42" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y42*AB42*R42,2)</f>
       </c>
       <c r="AD42" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC42-X42,2)</f>
       </c>
       <c r="AE42" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD42/AC42,0)</f>
       </c>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.25">
@@ -3401,53 +3041,43 @@
         <v>0</v>
       </c>
       <c r="S43" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q43*R43,2)</f>
       </c>
       <c r="T43" s="5">
         <v>0</v>
       </c>
       <c r="U43" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S43*(1-T43),2)</f>
       </c>
       <c r="V43" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W43" s="11">
         <f>IFERROR(VLOOKUP(V43,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X43" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U43*W43,2)</f>
       </c>
       <c r="Y43" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q43</f>
       </c>
       <c r="Z43" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y43*R43,2)</f>
       </c>
       <c r="AA43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB43" s="11">
         <f>IFERROR(VLOOKUP(AA43,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC43" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y43*AB43*R43,2)</f>
       </c>
       <c r="AD43" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC43-X43,2)</f>
       </c>
       <c r="AE43" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD43/AC43,0)</f>
       </c>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.25">
@@ -3469,53 +3099,43 @@
         <v>0</v>
       </c>
       <c r="S44" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q44*R44,2)</f>
       </c>
       <c r="T44" s="5">
         <v>0</v>
       </c>
       <c r="U44" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S44*(1-T44),2)</f>
       </c>
       <c r="V44" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W44" s="11">
         <f>IFERROR(VLOOKUP(V44,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X44" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U44*W44,2)</f>
       </c>
       <c r="Y44" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q44</f>
       </c>
       <c r="Z44" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y44*R44,2)</f>
       </c>
       <c r="AA44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB44" s="11">
         <f>IFERROR(VLOOKUP(AA44,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC44" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y44*AB44*R44,2)</f>
       </c>
       <c r="AD44" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC44-X44,2)</f>
       </c>
       <c r="AE44" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD44/AC44,0)</f>
       </c>
     </row>
     <row r="45" spans="2:31" x14ac:dyDescent="0.25">
@@ -3537,53 +3157,43 @@
         <v>0</v>
       </c>
       <c r="S45" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q45*R45,2)</f>
       </c>
       <c r="T45" s="5">
         <v>0</v>
       </c>
       <c r="U45" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S45*(1-T45),2)</f>
       </c>
       <c r="V45" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W45" s="11">
         <f>IFERROR(VLOOKUP(V45,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X45" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U45*W45,2)</f>
       </c>
       <c r="Y45" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q45</f>
       </c>
       <c r="Z45" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y45*R45,2)</f>
       </c>
       <c r="AA45" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB45" s="11">
         <f>IFERROR(VLOOKUP(AA45,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC45" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y45*AB45*R45,2)</f>
       </c>
       <c r="AD45" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC45-X45,2)</f>
       </c>
       <c r="AE45" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD45/AC45,0)</f>
       </c>
     </row>
     <row r="46" spans="2:31" x14ac:dyDescent="0.25">
@@ -3605,53 +3215,43 @@
         <v>0</v>
       </c>
       <c r="S46" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q46*R46,2)</f>
       </c>
       <c r="T46" s="5">
         <v>0</v>
       </c>
       <c r="U46" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S46*(1-T46),2)</f>
       </c>
       <c r="V46" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W46" s="11">
         <f>IFERROR(VLOOKUP(V46,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X46" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U46*W46,2)</f>
       </c>
       <c r="Y46" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q46</f>
       </c>
       <c r="Z46" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y46*R46,2)</f>
       </c>
       <c r="AA46" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB46" s="11">
         <f>IFERROR(VLOOKUP(AA46,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC46" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y46*AB46*R46,2)</f>
       </c>
       <c r="AD46" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC46-X46,2)</f>
       </c>
       <c r="AE46" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD46/AC46,0)</f>
       </c>
     </row>
     <row r="47" spans="2:31" x14ac:dyDescent="0.25">
@@ -3673,53 +3273,43 @@
         <v>0</v>
       </c>
       <c r="S47" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q47*R47,2)</f>
       </c>
       <c r="T47" s="5">
         <v>0</v>
       </c>
       <c r="U47" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S47*(1-T47),2)</f>
       </c>
       <c r="V47" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W47" s="11">
         <f>IFERROR(VLOOKUP(V47,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X47" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U47*W47,2)</f>
       </c>
       <c r="Y47" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q47</f>
       </c>
       <c r="Z47" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y47*R47,2)</f>
       </c>
       <c r="AA47" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB47" s="11">
         <f>IFERROR(VLOOKUP(AA47,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC47" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y47*AB47*R47,2)</f>
       </c>
       <c r="AD47" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC47-X47,2)</f>
       </c>
       <c r="AE47" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD47/AC47,0)</f>
       </c>
     </row>
     <row r="48" spans="2:31" x14ac:dyDescent="0.25">
@@ -3741,53 +3331,43 @@
         <v>0</v>
       </c>
       <c r="S48" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q48*R48,2)</f>
       </c>
       <c r="T48" s="5">
         <v>0</v>
       </c>
       <c r="U48" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S48*(1-T48),2)</f>
       </c>
       <c r="V48" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W48" s="11">
         <f>IFERROR(VLOOKUP(V48,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X48" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U48*W48,2)</f>
       </c>
       <c r="Y48" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q48</f>
       </c>
       <c r="Z48" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y48*R48,2)</f>
       </c>
       <c r="AA48" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB48" s="11">
         <f>IFERROR(VLOOKUP(AA48,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC48" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y48*AB48*R48,2)</f>
       </c>
       <c r="AD48" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC48-X48,2)</f>
       </c>
       <c r="AE48" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD48/AC48,0)</f>
       </c>
     </row>
     <row r="49" spans="2:31" x14ac:dyDescent="0.25">
@@ -3809,53 +3389,43 @@
         <v>0</v>
       </c>
       <c r="S49" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q49*R49,2)</f>
       </c>
       <c r="T49" s="5">
         <v>0</v>
       </c>
       <c r="U49" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S49*(1-T49),2)</f>
       </c>
       <c r="V49" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W49" s="11">
         <f>IFERROR(VLOOKUP(V49,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X49" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U49*W49,2)</f>
       </c>
       <c r="Y49" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q49</f>
       </c>
       <c r="Z49" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y49*R49,2)</f>
       </c>
       <c r="AA49" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB49" s="11">
         <f>IFERROR(VLOOKUP(AA49,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC49" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y49*AB49*R49,2)</f>
       </c>
       <c r="AD49" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC49-X49,2)</f>
       </c>
       <c r="AE49" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD49/AC49,0)</f>
       </c>
     </row>
     <row r="50" spans="2:31" x14ac:dyDescent="0.25">
@@ -3877,53 +3447,43 @@
         <v>0</v>
       </c>
       <c r="S50" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q50*R50,2)</f>
       </c>
       <c r="T50" s="5">
         <v>0</v>
       </c>
       <c r="U50" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S50*(1-T50),2)</f>
       </c>
       <c r="V50" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W50" s="11">
         <f>IFERROR(VLOOKUP(V50,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X50" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U50*W50,2)</f>
       </c>
       <c r="Y50" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q50</f>
       </c>
       <c r="Z50" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y50*R50,2)</f>
       </c>
       <c r="AA50" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB50" s="11">
         <f>IFERROR(VLOOKUP(AA50,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC50" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y50*AB50*R50,2)</f>
       </c>
       <c r="AD50" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC50-X50,2)</f>
       </c>
       <c r="AE50" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD50/AC50,0)</f>
       </c>
     </row>
     <row r="51" spans="2:31" x14ac:dyDescent="0.25">
@@ -3945,53 +3505,43 @@
         <v>0</v>
       </c>
       <c r="S51" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q51*R51,2)</f>
       </c>
       <c r="T51" s="5">
         <v>0</v>
       </c>
       <c r="U51" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S51*(1-T51),2)</f>
       </c>
       <c r="V51" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W51" s="11">
         <f>IFERROR(VLOOKUP(V51,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X51" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U51*W51,2)</f>
       </c>
       <c r="Y51" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q51</f>
       </c>
       <c r="Z51" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y51*R51,2)</f>
       </c>
       <c r="AA51" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB51" s="11">
         <f>IFERROR(VLOOKUP(AA51,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC51" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y51*AB51*R51,2)</f>
       </c>
       <c r="AD51" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC51-X51,2)</f>
       </c>
       <c r="AE51" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD51/AC51,0)</f>
       </c>
     </row>
     <row r="52" spans="2:31" x14ac:dyDescent="0.25">
@@ -4013,53 +3563,43 @@
         <v>0</v>
       </c>
       <c r="S52" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q52*R52,2)</f>
       </c>
       <c r="T52" s="5">
         <v>0</v>
       </c>
       <c r="U52" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S52*(1-T52),2)</f>
       </c>
       <c r="V52" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W52" s="11">
         <f>IFERROR(VLOOKUP(V52,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X52" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U52*W52,2)</f>
       </c>
       <c r="Y52" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q52</f>
       </c>
       <c r="Z52" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y52*R52,2)</f>
       </c>
       <c r="AA52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB52" s="11">
         <f>IFERROR(VLOOKUP(AA52,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC52" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y52*AB52*R52,2)</f>
       </c>
       <c r="AD52" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC52-X52,2)</f>
       </c>
       <c r="AE52" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD52/AC52,0)</f>
       </c>
     </row>
     <row r="53" spans="2:31" x14ac:dyDescent="0.25">
@@ -4081,53 +3621,43 @@
         <v>0</v>
       </c>
       <c r="S53" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q53*R53,2)</f>
       </c>
       <c r="T53" s="5">
         <v>0</v>
       </c>
       <c r="U53" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S53*(1-T53),2)</f>
       </c>
       <c r="V53" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W53" s="11">
         <f>IFERROR(VLOOKUP(V53,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X53" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U53*W53,2)</f>
       </c>
       <c r="Y53" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q53</f>
       </c>
       <c r="Z53" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y53*R53,2)</f>
       </c>
       <c r="AA53" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB53" s="11">
         <f>IFERROR(VLOOKUP(AA53,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC53" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y53*AB53*R53,2)</f>
       </c>
       <c r="AD53" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC53-X53,2)</f>
       </c>
       <c r="AE53" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD53/AC53,0)</f>
       </c>
     </row>
     <row r="54" spans="2:31" x14ac:dyDescent="0.25">
@@ -4149,53 +3679,43 @@
         <v>0</v>
       </c>
       <c r="S54" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q54*R54,2)</f>
       </c>
       <c r="T54" s="5">
         <v>0</v>
       </c>
       <c r="U54" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S54*(1-T54),2)</f>
       </c>
       <c r="V54" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W54" s="11">
         <f>IFERROR(VLOOKUP(V54,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X54" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U54*W54,2)</f>
       </c>
       <c r="Y54" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q54</f>
       </c>
       <c r="Z54" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y54*R54,2)</f>
       </c>
       <c r="AA54" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB54" s="11">
         <f>IFERROR(VLOOKUP(AA54,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC54" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y54*AB54*R54,2)</f>
       </c>
       <c r="AD54" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC54-X54,2)</f>
       </c>
       <c r="AE54" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD54/AC54,0)</f>
       </c>
     </row>
     <row r="55" spans="2:31" x14ac:dyDescent="0.25">
@@ -4217,53 +3737,43 @@
         <v>0</v>
       </c>
       <c r="S55" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q55*R55,2)</f>
       </c>
       <c r="T55" s="5">
         <v>0</v>
       </c>
       <c r="U55" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S55*(1-T55),2)</f>
       </c>
       <c r="V55" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W55" s="11">
         <f>IFERROR(VLOOKUP(V55,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X55" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U55*W55,2)</f>
       </c>
       <c r="Y55" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q55</f>
       </c>
       <c r="Z55" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y55*R55,2)</f>
       </c>
       <c r="AA55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB55" s="11">
         <f>IFERROR(VLOOKUP(AA55,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC55" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y55*AB55*R55,2)</f>
       </c>
       <c r="AD55" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC55-X55,2)</f>
       </c>
       <c r="AE55" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD55/AC55,0)</f>
       </c>
     </row>
     <row r="56" spans="2:31" x14ac:dyDescent="0.25">
@@ -4285,53 +3795,43 @@
         <v>0</v>
       </c>
       <c r="S56" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q56*R56,2)</f>
       </c>
       <c r="T56" s="5">
         <v>0</v>
       </c>
       <c r="U56" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S56*(1-T56),2)</f>
       </c>
       <c r="V56" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W56" s="11">
         <f>IFERROR(VLOOKUP(V56,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X56" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U56*W56,2)</f>
       </c>
       <c r="Y56" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q56</f>
       </c>
       <c r="Z56" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y56*R56,2)</f>
       </c>
       <c r="AA56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB56" s="11">
         <f>IFERROR(VLOOKUP(AA56,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC56" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y56*AB56*R56,2)</f>
       </c>
       <c r="AD56" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC56-X56,2)</f>
       </c>
       <c r="AE56" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD56/AC56,0)</f>
       </c>
     </row>
     <row r="57" spans="2:31" x14ac:dyDescent="0.25">
@@ -4353,53 +3853,43 @@
         <v>0</v>
       </c>
       <c r="S57" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q57*R57,2)</f>
       </c>
       <c r="T57" s="5">
         <v>0</v>
       </c>
       <c r="U57" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S57*(1-T57),2)</f>
       </c>
       <c r="V57" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W57" s="11">
         <f>IFERROR(VLOOKUP(V57,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X57" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U57*W57,2)</f>
       </c>
       <c r="Y57" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q57</f>
       </c>
       <c r="Z57" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y57*R57,2)</f>
       </c>
       <c r="AA57" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB57" s="11">
         <f>IFERROR(VLOOKUP(AA57,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC57" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y57*AB57*R57,2)</f>
       </c>
       <c r="AD57" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC57-X57,2)</f>
       </c>
       <c r="AE57" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD57/AC57,0)</f>
       </c>
     </row>
     <row r="58" spans="2:31" x14ac:dyDescent="0.25">
@@ -4421,53 +3911,43 @@
         <v>0</v>
       </c>
       <c r="S58" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q58*R58,2)</f>
       </c>
       <c r="T58" s="5">
         <v>0</v>
       </c>
       <c r="U58" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S58*(1-T58),2)</f>
       </c>
       <c r="V58" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W58" s="11">
         <f>IFERROR(VLOOKUP(V58,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X58" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U58*W58,2)</f>
       </c>
       <c r="Y58" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q58</f>
       </c>
       <c r="Z58" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y58*R58,2)</f>
       </c>
       <c r="AA58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB58" s="11">
         <f>IFERROR(VLOOKUP(AA58,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC58" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y58*AB58*R58,2)</f>
       </c>
       <c r="AD58" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC58-X58,2)</f>
       </c>
       <c r="AE58" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD58/AC58,0)</f>
       </c>
     </row>
     <row r="59" spans="2:31" x14ac:dyDescent="0.25">
@@ -4489,53 +3969,43 @@
         <v>0</v>
       </c>
       <c r="S59" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q59*R59,2)</f>
       </c>
       <c r="T59" s="5">
         <v>0</v>
       </c>
       <c r="U59" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S59*(1-T59),2)</f>
       </c>
       <c r="V59" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W59" s="11">
         <f>IFERROR(VLOOKUP(V59,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X59" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U59*W59,2)</f>
       </c>
       <c r="Y59" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q59</f>
       </c>
       <c r="Z59" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y59*R59,2)</f>
       </c>
       <c r="AA59" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB59" s="11">
         <f>IFERROR(VLOOKUP(AA59,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC59" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y59*AB59*R59,2)</f>
       </c>
       <c r="AD59" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC59-X59,2)</f>
       </c>
       <c r="AE59" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD59/AC59,0)</f>
       </c>
     </row>
     <row r="60" spans="2:31" x14ac:dyDescent="0.25">
@@ -4557,53 +4027,43 @@
         <v>0</v>
       </c>
       <c r="S60" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q60*R60,2)</f>
       </c>
       <c r="T60" s="5">
         <v>0</v>
       </c>
       <c r="U60" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S60*(1-T60),2)</f>
       </c>
       <c r="V60" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W60" s="11">
         <f>IFERROR(VLOOKUP(V60,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X60" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U60*W60,2)</f>
       </c>
       <c r="Y60" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q60</f>
       </c>
       <c r="Z60" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y60*R60,2)</f>
       </c>
       <c r="AA60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB60" s="11">
         <f>IFERROR(VLOOKUP(AA60,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC60" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y60*AB60*R60,2)</f>
       </c>
       <c r="AD60" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC60-X60,2)</f>
       </c>
       <c r="AE60" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD60/AC60,0)</f>
       </c>
     </row>
     <row r="61" spans="2:31" x14ac:dyDescent="0.25">
@@ -4625,53 +4085,43 @@
         <v>0</v>
       </c>
       <c r="S61" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q61*R61,2)</f>
       </c>
       <c r="T61" s="5">
         <v>0</v>
       </c>
       <c r="U61" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S61*(1-T61),2)</f>
       </c>
       <c r="V61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W61" s="11">
         <f>IFERROR(VLOOKUP(V61,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X61" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U61*W61,2)</f>
       </c>
       <c r="Y61" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q61</f>
       </c>
       <c r="Z61" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y61*R61,2)</f>
       </c>
       <c r="AA61" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB61" s="11">
         <f>IFERROR(VLOOKUP(AA61,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC61" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y61*AB61*R61,2)</f>
       </c>
       <c r="AD61" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC61-X61,2)</f>
       </c>
       <c r="AE61" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD61/AC61,0)</f>
       </c>
     </row>
     <row r="62" spans="2:31" x14ac:dyDescent="0.25">
@@ -4693,53 +4143,43 @@
         <v>0</v>
       </c>
       <c r="S62" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q62*R62,2)</f>
       </c>
       <c r="T62" s="5">
         <v>0</v>
       </c>
       <c r="U62" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S62*(1-T62),2)</f>
       </c>
       <c r="V62" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W62" s="11">
         <f>IFERROR(VLOOKUP(V62,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X62" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U62*W62,2)</f>
       </c>
       <c r="Y62" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q62</f>
       </c>
       <c r="Z62" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y62*R62,2)</f>
       </c>
       <c r="AA62" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB62" s="11">
         <f>IFERROR(VLOOKUP(AA62,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC62" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y62*AB62*R62,2)</f>
       </c>
       <c r="AD62" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC62-X62,2)</f>
       </c>
       <c r="AE62" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD62/AC62,0)</f>
       </c>
     </row>
     <row r="63" spans="2:31" x14ac:dyDescent="0.25">
@@ -4761,53 +4201,43 @@
         <v>0</v>
       </c>
       <c r="S63" s="12">
-        <f t="shared" ref="S63:S98" si="22">+Q63*R63</f>
-        <v>0</v>
+        <f>ROUND(Q63*R63,2)</f>
       </c>
       <c r="T63" s="5">
         <v>0</v>
       </c>
       <c r="U63" s="12">
-        <f t="shared" ref="U63:U98" si="23">S63*(1-T63)</f>
-        <v>0</v>
+        <f>ROUND(S63*(1-T63),2)</f>
       </c>
       <c r="V63" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W63" s="11">
         <f>IFERROR(VLOOKUP(V63,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X63" s="12">
-        <f t="shared" ref="X63:X98" si="24">U63*W63</f>
-        <v>0</v>
+        <f>ROUND(U63*W63,2)</f>
       </c>
       <c r="Y63" s="26">
-        <f t="shared" ref="Y63:Y98" si="25">Q63</f>
-        <v>0</v>
+        <f>Q63</f>
       </c>
       <c r="Z63" s="12">
-        <f t="shared" ref="Z63:Z98" si="26">+Y63*R63</f>
-        <v>0</v>
+        <f>ROUND(Y63*R63,2)</f>
       </c>
       <c r="AA63" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB63" s="11">
         <f>IFERROR(VLOOKUP(AA63,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC63" s="12">
-        <f t="shared" ref="AC63:AC98" si="27">+Y63*AB63*R63</f>
-        <v>0</v>
+        <f>ROUND(Y63*AB63*R63,2)</f>
       </c>
       <c r="AD63" s="12">
-        <f t="shared" ref="AD63:AD98" si="28">+AC63-X63</f>
-        <v>0</v>
+        <f>ROUND(AC63-X63,2)</f>
       </c>
       <c r="AE63" s="13">
-        <f t="shared" ref="AE63:AE98" si="29">IFERROR(AD63/AC63,0)</f>
-        <v>0</v>
+        <f>IFERROR(AD63/AC63,0)</f>
       </c>
     </row>
     <row r="64" spans="2:31" x14ac:dyDescent="0.25">
@@ -4829,53 +4259,43 @@
         <v>0</v>
       </c>
       <c r="S64" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q64*R64,2)</f>
       </c>
       <c r="T64" s="5">
         <v>0</v>
       </c>
       <c r="U64" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S64*(1-T64),2)</f>
       </c>
       <c r="V64" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W64" s="11">
         <f>IFERROR(VLOOKUP(V64,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X64" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U64*W64,2)</f>
       </c>
       <c r="Y64" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q64</f>
       </c>
       <c r="Z64" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y64*R64,2)</f>
       </c>
       <c r="AA64" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB64" s="11">
         <f>IFERROR(VLOOKUP(AA64,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC64" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y64*AB64*R64,2)</f>
       </c>
       <c r="AD64" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC64-X64,2)</f>
       </c>
       <c r="AE64" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD64/AC64,0)</f>
       </c>
     </row>
     <row r="65" spans="2:31" x14ac:dyDescent="0.25">
@@ -4897,53 +4317,43 @@
         <v>0</v>
       </c>
       <c r="S65" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q65*R65,2)</f>
       </c>
       <c r="T65" s="5">
         <v>0</v>
       </c>
       <c r="U65" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S65*(1-T65),2)</f>
       </c>
       <c r="V65" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W65" s="11">
         <f>IFERROR(VLOOKUP(V65,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X65" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U65*W65,2)</f>
       </c>
       <c r="Y65" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q65</f>
       </c>
       <c r="Z65" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y65*R65,2)</f>
       </c>
       <c r="AA65" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB65" s="11">
         <f>IFERROR(VLOOKUP(AA65,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC65" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y65*AB65*R65,2)</f>
       </c>
       <c r="AD65" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC65-X65,2)</f>
       </c>
       <c r="AE65" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD65/AC65,0)</f>
       </c>
     </row>
     <row r="66" spans="2:31" x14ac:dyDescent="0.25">
@@ -4965,53 +4375,43 @@
         <v>0</v>
       </c>
       <c r="S66" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q66*R66,2)</f>
       </c>
       <c r="T66" s="5">
         <v>0</v>
       </c>
       <c r="U66" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S66*(1-T66),2)</f>
       </c>
       <c r="V66" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W66" s="11">
         <f>IFERROR(VLOOKUP(V66,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X66" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U66*W66,2)</f>
       </c>
       <c r="Y66" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q66</f>
       </c>
       <c r="Z66" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y66*R66,2)</f>
       </c>
       <c r="AA66" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB66" s="11">
         <f>IFERROR(VLOOKUP(AA66,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC66" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y66*AB66*R66,2)</f>
       </c>
       <c r="AD66" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC66-X66,2)</f>
       </c>
       <c r="AE66" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD66/AC66,0)</f>
       </c>
     </row>
     <row r="67" spans="2:31" x14ac:dyDescent="0.25">
@@ -5033,53 +4433,43 @@
         <v>0</v>
       </c>
       <c r="S67" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q67*R67,2)</f>
       </c>
       <c r="T67" s="5">
         <v>0</v>
       </c>
       <c r="U67" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S67*(1-T67),2)</f>
       </c>
       <c r="V67" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W67" s="11">
         <f>IFERROR(VLOOKUP(V67,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X67" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U67*W67,2)</f>
       </c>
       <c r="Y67" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q67</f>
       </c>
       <c r="Z67" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y67*R67,2)</f>
       </c>
       <c r="AA67" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB67" s="11">
         <f>IFERROR(VLOOKUP(AA67,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC67" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y67*AB67*R67,2)</f>
       </c>
       <c r="AD67" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC67-X67,2)</f>
       </c>
       <c r="AE67" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD67/AC67,0)</f>
       </c>
     </row>
     <row r="68" spans="2:31" x14ac:dyDescent="0.25">
@@ -5101,53 +4491,43 @@
         <v>0</v>
       </c>
       <c r="S68" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q68*R68,2)</f>
       </c>
       <c r="T68" s="5">
         <v>0</v>
       </c>
       <c r="U68" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S68*(1-T68),2)</f>
       </c>
       <c r="V68" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W68" s="11">
         <f>IFERROR(VLOOKUP(V68,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X68" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U68*W68,2)</f>
       </c>
       <c r="Y68" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q68</f>
       </c>
       <c r="Z68" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y68*R68,2)</f>
       </c>
       <c r="AA68" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB68" s="11">
         <f>IFERROR(VLOOKUP(AA68,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC68" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y68*AB68*R68,2)</f>
       </c>
       <c r="AD68" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC68-X68,2)</f>
       </c>
       <c r="AE68" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD68/AC68,0)</f>
       </c>
     </row>
     <row r="69" spans="2:31" x14ac:dyDescent="0.25">
@@ -5169,53 +4549,43 @@
         <v>0</v>
       </c>
       <c r="S69" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q69*R69,2)</f>
       </c>
       <c r="T69" s="5">
         <v>0</v>
       </c>
       <c r="U69" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S69*(1-T69),2)</f>
       </c>
       <c r="V69" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W69" s="11">
         <f>IFERROR(VLOOKUP(V69,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X69" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U69*W69,2)</f>
       </c>
       <c r="Y69" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q69</f>
       </c>
       <c r="Z69" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y69*R69,2)</f>
       </c>
       <c r="AA69" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB69" s="11">
         <f>IFERROR(VLOOKUP(AA69,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC69" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y69*AB69*R69,2)</f>
       </c>
       <c r="AD69" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC69-X69,2)</f>
       </c>
       <c r="AE69" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD69/AC69,0)</f>
       </c>
     </row>
     <row r="70" spans="2:31" x14ac:dyDescent="0.25">
@@ -5237,53 +4607,43 @@
         <v>0</v>
       </c>
       <c r="S70" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q70*R70,2)</f>
       </c>
       <c r="T70" s="5">
         <v>0</v>
       </c>
       <c r="U70" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S70*(1-T70),2)</f>
       </c>
       <c r="V70" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W70" s="11">
         <f>IFERROR(VLOOKUP(V70,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X70" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U70*W70,2)</f>
       </c>
       <c r="Y70" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q70</f>
       </c>
       <c r="Z70" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y70*R70,2)</f>
       </c>
       <c r="AA70" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB70" s="11">
         <f>IFERROR(VLOOKUP(AA70,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC70" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y70*AB70*R70,2)</f>
       </c>
       <c r="AD70" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC70-X70,2)</f>
       </c>
       <c r="AE70" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD70/AC70,0)</f>
       </c>
     </row>
     <row r="71" spans="2:31" x14ac:dyDescent="0.25">
@@ -5305,53 +4665,43 @@
         <v>0</v>
       </c>
       <c r="S71" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q71*R71,2)</f>
       </c>
       <c r="T71" s="5">
         <v>0</v>
       </c>
       <c r="U71" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S71*(1-T71),2)</f>
       </c>
       <c r="V71" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W71" s="11">
         <f>IFERROR(VLOOKUP(V71,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X71" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U71*W71,2)</f>
       </c>
       <c r="Y71" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q71</f>
       </c>
       <c r="Z71" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y71*R71,2)</f>
       </c>
       <c r="AA71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB71" s="11">
         <f>IFERROR(VLOOKUP(AA71,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC71" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y71*AB71*R71,2)</f>
       </c>
       <c r="AD71" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC71-X71,2)</f>
       </c>
       <c r="AE71" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD71/AC71,0)</f>
       </c>
     </row>
     <row r="72" spans="2:31" x14ac:dyDescent="0.25">
@@ -5373,53 +4723,43 @@
         <v>0</v>
       </c>
       <c r="S72" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q72*R72,2)</f>
       </c>
       <c r="T72" s="5">
         <v>0</v>
       </c>
       <c r="U72" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S72*(1-T72),2)</f>
       </c>
       <c r="V72" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W72" s="11">
         <f>IFERROR(VLOOKUP(V72,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X72" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U72*W72,2)</f>
       </c>
       <c r="Y72" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q72</f>
       </c>
       <c r="Z72" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y72*R72,2)</f>
       </c>
       <c r="AA72" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB72" s="11">
         <f>IFERROR(VLOOKUP(AA72,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC72" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y72*AB72*R72,2)</f>
       </c>
       <c r="AD72" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC72-X72,2)</f>
       </c>
       <c r="AE72" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD72/AC72,0)</f>
       </c>
     </row>
     <row r="73" spans="2:31" x14ac:dyDescent="0.25">
@@ -5441,53 +4781,43 @@
         <v>0</v>
       </c>
       <c r="S73" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q73*R73,2)</f>
       </c>
       <c r="T73" s="5">
         <v>0</v>
       </c>
       <c r="U73" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S73*(1-T73),2)</f>
       </c>
       <c r="V73" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W73" s="11">
         <f>IFERROR(VLOOKUP(V73,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X73" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U73*W73,2)</f>
       </c>
       <c r="Y73" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q73</f>
       </c>
       <c r="Z73" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y73*R73,2)</f>
       </c>
       <c r="AA73" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB73" s="11">
         <f>IFERROR(VLOOKUP(AA73,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC73" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y73*AB73*R73,2)</f>
       </c>
       <c r="AD73" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC73-X73,2)</f>
       </c>
       <c r="AE73" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD73/AC73,0)</f>
       </c>
     </row>
     <row r="74" spans="2:31" x14ac:dyDescent="0.25">
@@ -5509,53 +4839,43 @@
         <v>0</v>
       </c>
       <c r="S74" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q74*R74,2)</f>
       </c>
       <c r="T74" s="5">
         <v>0</v>
       </c>
       <c r="U74" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S74*(1-T74),2)</f>
       </c>
       <c r="V74" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W74" s="11">
         <f>IFERROR(VLOOKUP(V74,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X74" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U74*W74,2)</f>
       </c>
       <c r="Y74" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q74</f>
       </c>
       <c r="Z74" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y74*R74,2)</f>
       </c>
       <c r="AA74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB74" s="11">
         <f>IFERROR(VLOOKUP(AA74,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC74" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y74*AB74*R74,2)</f>
       </c>
       <c r="AD74" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC74-X74,2)</f>
       </c>
       <c r="AE74" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD74/AC74,0)</f>
       </c>
     </row>
     <row r="75" spans="2:31" x14ac:dyDescent="0.25">
@@ -5577,53 +4897,43 @@
         <v>0</v>
       </c>
       <c r="S75" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q75*R75,2)</f>
       </c>
       <c r="T75" s="5">
         <v>0</v>
       </c>
       <c r="U75" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S75*(1-T75),2)</f>
       </c>
       <c r="V75" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W75" s="11">
         <f>IFERROR(VLOOKUP(V75,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X75" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U75*W75,2)</f>
       </c>
       <c r="Y75" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q75</f>
       </c>
       <c r="Z75" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y75*R75,2)</f>
       </c>
       <c r="AA75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB75" s="11">
         <f>IFERROR(VLOOKUP(AA75,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC75" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y75*AB75*R75,2)</f>
       </c>
       <c r="AD75" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC75-X75,2)</f>
       </c>
       <c r="AE75" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD75/AC75,0)</f>
       </c>
     </row>
     <row r="76" spans="2:31" x14ac:dyDescent="0.25">
@@ -5645,53 +4955,43 @@
         <v>0</v>
       </c>
       <c r="S76" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q76*R76,2)</f>
       </c>
       <c r="T76" s="5">
         <v>0</v>
       </c>
       <c r="U76" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S76*(1-T76),2)</f>
       </c>
       <c r="V76" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W76" s="11">
         <f>IFERROR(VLOOKUP(V76,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X76" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U76*W76,2)</f>
       </c>
       <c r="Y76" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q76</f>
       </c>
       <c r="Z76" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y76*R76,2)</f>
       </c>
       <c r="AA76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB76" s="11">
         <f>IFERROR(VLOOKUP(AA76,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC76" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y76*AB76*R76,2)</f>
       </c>
       <c r="AD76" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC76-X76,2)</f>
       </c>
       <c r="AE76" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD76/AC76,0)</f>
       </c>
     </row>
     <row r="77" spans="2:31" x14ac:dyDescent="0.25">
@@ -5713,53 +5013,43 @@
         <v>0</v>
       </c>
       <c r="S77" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q77*R77,2)</f>
       </c>
       <c r="T77" s="5">
         <v>0</v>
       </c>
       <c r="U77" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S77*(1-T77),2)</f>
       </c>
       <c r="V77" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W77" s="11">
         <f>IFERROR(VLOOKUP(V77,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X77" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U77*W77,2)</f>
       </c>
       <c r="Y77" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q77</f>
       </c>
       <c r="Z77" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y77*R77,2)</f>
       </c>
       <c r="AA77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB77" s="11">
         <f>IFERROR(VLOOKUP(AA77,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC77" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y77*AB77*R77,2)</f>
       </c>
       <c r="AD77" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC77-X77,2)</f>
       </c>
       <c r="AE77" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD77/AC77,0)</f>
       </c>
     </row>
     <row r="78" spans="2:31" x14ac:dyDescent="0.25">
@@ -5781,53 +5071,43 @@
         <v>0</v>
       </c>
       <c r="S78" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q78*R78,2)</f>
       </c>
       <c r="T78" s="5">
         <v>0</v>
       </c>
       <c r="U78" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S78*(1-T78),2)</f>
       </c>
       <c r="V78" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W78" s="11">
         <f>IFERROR(VLOOKUP(V78,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X78" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U78*W78,2)</f>
       </c>
       <c r="Y78" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q78</f>
       </c>
       <c r="Z78" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y78*R78,2)</f>
       </c>
       <c r="AA78" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB78" s="11">
         <f>IFERROR(VLOOKUP(AA78,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC78" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y78*AB78*R78,2)</f>
       </c>
       <c r="AD78" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC78-X78,2)</f>
       </c>
       <c r="AE78" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD78/AC78,0)</f>
       </c>
     </row>
     <row r="79" spans="2:31" x14ac:dyDescent="0.25">
@@ -5849,53 +5129,43 @@
         <v>0</v>
       </c>
       <c r="S79" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q79*R79,2)</f>
       </c>
       <c r="T79" s="5">
         <v>0</v>
       </c>
       <c r="U79" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S79*(1-T79),2)</f>
       </c>
       <c r="V79" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W79" s="11">
         <f>IFERROR(VLOOKUP(V79,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X79" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U79*W79,2)</f>
       </c>
       <c r="Y79" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q79</f>
       </c>
       <c r="Z79" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y79*R79,2)</f>
       </c>
       <c r="AA79" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB79" s="11">
         <f>IFERROR(VLOOKUP(AA79,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC79" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y79*AB79*R79,2)</f>
       </c>
       <c r="AD79" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC79-X79,2)</f>
       </c>
       <c r="AE79" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD79/AC79,0)</f>
       </c>
     </row>
     <row r="80" spans="2:31" x14ac:dyDescent="0.25">
@@ -5917,53 +5187,43 @@
         <v>0</v>
       </c>
       <c r="S80" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q80*R80,2)</f>
       </c>
       <c r="T80" s="5">
         <v>0</v>
       </c>
       <c r="U80" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S80*(1-T80),2)</f>
       </c>
       <c r="V80" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W80" s="11">
         <f>IFERROR(VLOOKUP(V80,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X80" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U80*W80,2)</f>
       </c>
       <c r="Y80" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q80</f>
       </c>
       <c r="Z80" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y80*R80,2)</f>
       </c>
       <c r="AA80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB80" s="11">
         <f>IFERROR(VLOOKUP(AA80,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC80" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y80*AB80*R80,2)</f>
       </c>
       <c r="AD80" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC80-X80,2)</f>
       </c>
       <c r="AE80" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD80/AC80,0)</f>
       </c>
     </row>
     <row r="81" spans="2:31" x14ac:dyDescent="0.25">
@@ -5985,53 +5245,43 @@
         <v>0</v>
       </c>
       <c r="S81" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q81*R81,2)</f>
       </c>
       <c r="T81" s="5">
         <v>0</v>
       </c>
       <c r="U81" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S81*(1-T81),2)</f>
       </c>
       <c r="V81" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W81" s="11">
         <f>IFERROR(VLOOKUP(V81,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X81" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U81*W81,2)</f>
       </c>
       <c r="Y81" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q81</f>
       </c>
       <c r="Z81" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y81*R81,2)</f>
       </c>
       <c r="AA81" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB81" s="11">
         <f>IFERROR(VLOOKUP(AA81,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC81" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y81*AB81*R81,2)</f>
       </c>
       <c r="AD81" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC81-X81,2)</f>
       </c>
       <c r="AE81" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD81/AC81,0)</f>
       </c>
     </row>
     <row r="82" spans="2:31" x14ac:dyDescent="0.25">
@@ -6053,53 +5303,43 @@
         <v>0</v>
       </c>
       <c r="S82" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q82*R82,2)</f>
       </c>
       <c r="T82" s="5">
         <v>0</v>
       </c>
       <c r="U82" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S82*(1-T82),2)</f>
       </c>
       <c r="V82" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W82" s="11">
         <f>IFERROR(VLOOKUP(V82,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X82" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U82*W82,2)</f>
       </c>
       <c r="Y82" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q82</f>
       </c>
       <c r="Z82" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y82*R82,2)</f>
       </c>
       <c r="AA82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB82" s="11">
         <f>IFERROR(VLOOKUP(AA82,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC82" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y82*AB82*R82,2)</f>
       </c>
       <c r="AD82" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC82-X82,2)</f>
       </c>
       <c r="AE82" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD82/AC82,0)</f>
       </c>
     </row>
     <row r="83" spans="2:31" x14ac:dyDescent="0.25">
@@ -6121,53 +5361,43 @@
         <v>0</v>
       </c>
       <c r="S83" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q83*R83,2)</f>
       </c>
       <c r="T83" s="5">
         <v>0</v>
       </c>
       <c r="U83" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S83*(1-T83),2)</f>
       </c>
       <c r="V83" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W83" s="11">
         <f>IFERROR(VLOOKUP(V83,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X83" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U83*W83,2)</f>
       </c>
       <c r="Y83" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q83</f>
       </c>
       <c r="Z83" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y83*R83,2)</f>
       </c>
       <c r="AA83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB83" s="11">
         <f>IFERROR(VLOOKUP(AA83,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC83" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y83*AB83*R83,2)</f>
       </c>
       <c r="AD83" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC83-X83,2)</f>
       </c>
       <c r="AE83" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD83/AC83,0)</f>
       </c>
     </row>
     <row r="84" spans="2:31" x14ac:dyDescent="0.25">
@@ -6189,53 +5419,43 @@
         <v>0</v>
       </c>
       <c r="S84" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q84*R84,2)</f>
       </c>
       <c r="T84" s="5">
         <v>0</v>
       </c>
       <c r="U84" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S84*(1-T84),2)</f>
       </c>
       <c r="V84" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W84" s="11">
         <f>IFERROR(VLOOKUP(V84,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X84" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U84*W84,2)</f>
       </c>
       <c r="Y84" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q84</f>
       </c>
       <c r="Z84" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y84*R84,2)</f>
       </c>
       <c r="AA84" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB84" s="11">
         <f>IFERROR(VLOOKUP(AA84,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC84" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y84*AB84*R84,2)</f>
       </c>
       <c r="AD84" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC84-X84,2)</f>
       </c>
       <c r="AE84" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD84/AC84,0)</f>
       </c>
     </row>
     <row r="85" spans="2:31" x14ac:dyDescent="0.25">
@@ -6257,53 +5477,43 @@
         <v>0</v>
       </c>
       <c r="S85" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q85*R85,2)</f>
       </c>
       <c r="T85" s="5">
         <v>0</v>
       </c>
       <c r="U85" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S85*(1-T85),2)</f>
       </c>
       <c r="V85" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W85" s="11">
         <f>IFERROR(VLOOKUP(V85,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X85" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U85*W85,2)</f>
       </c>
       <c r="Y85" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q85</f>
       </c>
       <c r="Z85" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y85*R85,2)</f>
       </c>
       <c r="AA85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB85" s="11">
         <f>IFERROR(VLOOKUP(AA85,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC85" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y85*AB85*R85,2)</f>
       </c>
       <c r="AD85" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC85-X85,2)</f>
       </c>
       <c r="AE85" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD85/AC85,0)</f>
       </c>
     </row>
     <row r="86" spans="2:31" x14ac:dyDescent="0.25">
@@ -6325,53 +5535,43 @@
         <v>0</v>
       </c>
       <c r="S86" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q86*R86,2)</f>
       </c>
       <c r="T86" s="5">
         <v>0</v>
       </c>
       <c r="U86" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S86*(1-T86),2)</f>
       </c>
       <c r="V86" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W86" s="11">
         <f>IFERROR(VLOOKUP(V86,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X86" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U86*W86,2)</f>
       </c>
       <c r="Y86" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q86</f>
       </c>
       <c r="Z86" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y86*R86,2)</f>
       </c>
       <c r="AA86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB86" s="11">
         <f>IFERROR(VLOOKUP(AA86,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC86" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y86*AB86*R86,2)</f>
       </c>
       <c r="AD86" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC86-X86,2)</f>
       </c>
       <c r="AE86" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD86/AC86,0)</f>
       </c>
     </row>
     <row r="87" spans="2:31" x14ac:dyDescent="0.25">
@@ -6393,53 +5593,43 @@
         <v>0</v>
       </c>
       <c r="S87" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q87*R87,2)</f>
       </c>
       <c r="T87" s="5">
         <v>0</v>
       </c>
       <c r="U87" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S87*(1-T87),2)</f>
       </c>
       <c r="V87" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W87" s="11">
         <f>IFERROR(VLOOKUP(V87,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X87" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U87*W87,2)</f>
       </c>
       <c r="Y87" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q87</f>
       </c>
       <c r="Z87" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y87*R87,2)</f>
       </c>
       <c r="AA87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB87" s="11">
         <f>IFERROR(VLOOKUP(AA87,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC87" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y87*AB87*R87,2)</f>
       </c>
       <c r="AD87" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC87-X87,2)</f>
       </c>
       <c r="AE87" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD87/AC87,0)</f>
       </c>
     </row>
     <row r="88" spans="2:31" x14ac:dyDescent="0.25">
@@ -6461,53 +5651,43 @@
         <v>0</v>
       </c>
       <c r="S88" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q88*R88,2)</f>
       </c>
       <c r="T88" s="5">
         <v>0</v>
       </c>
       <c r="U88" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S88*(1-T88),2)</f>
       </c>
       <c r="V88" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W88" s="11">
         <f>IFERROR(VLOOKUP(V88,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X88" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U88*W88,2)</f>
       </c>
       <c r="Y88" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q88</f>
       </c>
       <c r="Z88" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y88*R88,2)</f>
       </c>
       <c r="AA88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB88" s="11">
         <f>IFERROR(VLOOKUP(AA88,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC88" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y88*AB88*R88,2)</f>
       </c>
       <c r="AD88" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC88-X88,2)</f>
       </c>
       <c r="AE88" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD88/AC88,0)</f>
       </c>
     </row>
     <row r="89" spans="2:31" x14ac:dyDescent="0.25">
@@ -6529,53 +5709,43 @@
         <v>0</v>
       </c>
       <c r="S89" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q89*R89,2)</f>
       </c>
       <c r="T89" s="5">
         <v>0</v>
       </c>
       <c r="U89" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S89*(1-T89),2)</f>
       </c>
       <c r="V89" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W89" s="11">
         <f>IFERROR(VLOOKUP(V89,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X89" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U89*W89,2)</f>
       </c>
       <c r="Y89" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q89</f>
       </c>
       <c r="Z89" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y89*R89,2)</f>
       </c>
       <c r="AA89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB89" s="11">
         <f>IFERROR(VLOOKUP(AA89,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC89" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y89*AB89*R89,2)</f>
       </c>
       <c r="AD89" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC89-X89,2)</f>
       </c>
       <c r="AE89" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD89/AC89,0)</f>
       </c>
     </row>
     <row r="90" spans="2:31" x14ac:dyDescent="0.25">
@@ -6597,53 +5767,43 @@
         <v>0</v>
       </c>
       <c r="S90" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q90*R90,2)</f>
       </c>
       <c r="T90" s="5">
         <v>0</v>
       </c>
       <c r="U90" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S90*(1-T90),2)</f>
       </c>
       <c r="V90" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W90" s="11">
         <f>IFERROR(VLOOKUP(V90,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X90" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U90*W90,2)</f>
       </c>
       <c r="Y90" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q90</f>
       </c>
       <c r="Z90" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y90*R90,2)</f>
       </c>
       <c r="AA90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB90" s="11">
         <f>IFERROR(VLOOKUP(AA90,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC90" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y90*AB90*R90,2)</f>
       </c>
       <c r="AD90" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC90-X90,2)</f>
       </c>
       <c r="AE90" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD90/AC90,0)</f>
       </c>
     </row>
     <row r="91" spans="2:31" x14ac:dyDescent="0.25">
@@ -6665,53 +5825,43 @@
         <v>0</v>
       </c>
       <c r="S91" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q91*R91,2)</f>
       </c>
       <c r="T91" s="5">
         <v>0</v>
       </c>
       <c r="U91" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S91*(1-T91),2)</f>
       </c>
       <c r="V91" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W91" s="11">
         <f>IFERROR(VLOOKUP(V91,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X91" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U91*W91,2)</f>
       </c>
       <c r="Y91" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q91</f>
       </c>
       <c r="Z91" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y91*R91,2)</f>
       </c>
       <c r="AA91" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB91" s="11">
         <f>IFERROR(VLOOKUP(AA91,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC91" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y91*AB91*R91,2)</f>
       </c>
       <c r="AD91" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC91-X91,2)</f>
       </c>
       <c r="AE91" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD91/AC91,0)</f>
       </c>
     </row>
     <row r="92" spans="2:31" x14ac:dyDescent="0.25">
@@ -6733,53 +5883,43 @@
         <v>0</v>
       </c>
       <c r="S92" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q92*R92,2)</f>
       </c>
       <c r="T92" s="5">
         <v>0</v>
       </c>
       <c r="U92" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S92*(1-T92),2)</f>
       </c>
       <c r="V92" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W92" s="11">
         <f>IFERROR(VLOOKUP(V92,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X92" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U92*W92,2)</f>
       </c>
       <c r="Y92" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q92</f>
       </c>
       <c r="Z92" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y92*R92,2)</f>
       </c>
       <c r="AA92" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB92" s="11">
         <f>IFERROR(VLOOKUP(AA92,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC92" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y92*AB92*R92,2)</f>
       </c>
       <c r="AD92" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC92-X92,2)</f>
       </c>
       <c r="AE92" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD92/AC92,0)</f>
       </c>
     </row>
     <row r="93" spans="2:31" x14ac:dyDescent="0.25">
@@ -6801,53 +5941,43 @@
         <v>0</v>
       </c>
       <c r="S93" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q93*R93,2)</f>
       </c>
       <c r="T93" s="5">
         <v>0</v>
       </c>
       <c r="U93" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S93*(1-T93),2)</f>
       </c>
       <c r="V93" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W93" s="11">
         <f>IFERROR(VLOOKUP(V93,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X93" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U93*W93,2)</f>
       </c>
       <c r="Y93" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q93</f>
       </c>
       <c r="Z93" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y93*R93,2)</f>
       </c>
       <c r="AA93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB93" s="11">
         <f>IFERROR(VLOOKUP(AA93,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC93" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y93*AB93*R93,2)</f>
       </c>
       <c r="AD93" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC93-X93,2)</f>
       </c>
       <c r="AE93" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD93/AC93,0)</f>
       </c>
     </row>
     <row r="94" spans="2:31" x14ac:dyDescent="0.25">
@@ -6869,53 +5999,43 @@
         <v>0</v>
       </c>
       <c r="S94" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q94*R94,2)</f>
       </c>
       <c r="T94" s="5">
         <v>0</v>
       </c>
       <c r="U94" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S94*(1-T94),2)</f>
       </c>
       <c r="V94" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W94" s="11">
         <f>IFERROR(VLOOKUP(V94,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X94" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U94*W94,2)</f>
       </c>
       <c r="Y94" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q94</f>
       </c>
       <c r="Z94" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y94*R94,2)</f>
       </c>
       <c r="AA94" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB94" s="11">
         <f>IFERROR(VLOOKUP(AA94,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC94" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y94*AB94*R94,2)</f>
       </c>
       <c r="AD94" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC94-X94,2)</f>
       </c>
       <c r="AE94" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD94/AC94,0)</f>
       </c>
     </row>
     <row r="95" spans="2:31" x14ac:dyDescent="0.25">
@@ -6937,53 +6057,43 @@
         <v>0</v>
       </c>
       <c r="S95" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q95*R95,2)</f>
       </c>
       <c r="T95" s="5">
         <v>0</v>
       </c>
       <c r="U95" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S95*(1-T95),2)</f>
       </c>
       <c r="V95" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W95" s="11">
         <f>IFERROR(VLOOKUP(V95,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X95" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U95*W95,2)</f>
       </c>
       <c r="Y95" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q95</f>
       </c>
       <c r="Z95" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y95*R95,2)</f>
       </c>
       <c r="AA95" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB95" s="11">
         <f>IFERROR(VLOOKUP(AA95,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC95" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y95*AB95*R95,2)</f>
       </c>
       <c r="AD95" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC95-X95,2)</f>
       </c>
       <c r="AE95" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD95/AC95,0)</f>
       </c>
     </row>
     <row r="96" spans="2:31" x14ac:dyDescent="0.25">
@@ -7005,53 +6115,43 @@
         <v>0</v>
       </c>
       <c r="S96" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q96*R96,2)</f>
       </c>
       <c r="T96" s="5">
         <v>0</v>
       </c>
       <c r="U96" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S96*(1-T96),2)</f>
       </c>
       <c r="V96" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W96" s="11">
         <f>IFERROR(VLOOKUP(V96,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X96" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U96*W96,2)</f>
       </c>
       <c r="Y96" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q96</f>
       </c>
       <c r="Z96" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y96*R96,2)</f>
       </c>
       <c r="AA96" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB96" s="11">
         <f>IFERROR(VLOOKUP(AA96,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC96" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y96*AB96*R96,2)</f>
       </c>
       <c r="AD96" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC96-X96,2)</f>
       </c>
       <c r="AE96" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD96/AC96,0)</f>
       </c>
     </row>
     <row r="97" spans="2:36" x14ac:dyDescent="0.25">
@@ -7073,53 +6173,43 @@
         <v>0</v>
       </c>
       <c r="S97" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q97*R97,2)</f>
       </c>
       <c r="T97" s="5">
         <v>0</v>
       </c>
       <c r="U97" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S97*(1-T97),2)</f>
       </c>
       <c r="V97" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W97" s="11">
         <f>IFERROR(VLOOKUP(V97,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X97" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U97*W97,2)</f>
       </c>
       <c r="Y97" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q97</f>
       </c>
       <c r="Z97" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y97*R97,2)</f>
       </c>
       <c r="AA97" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB97" s="11">
         <f>IFERROR(VLOOKUP(AA97,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC97" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y97*AB97*R97,2)</f>
       </c>
       <c r="AD97" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC97-X97,2)</f>
       </c>
       <c r="AE97" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD97/AC97,0)</f>
       </c>
     </row>
     <row r="98" spans="2:36" x14ac:dyDescent="0.25">
@@ -7141,53 +6231,43 @@
         <v>0</v>
       </c>
       <c r="S98" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f>ROUND(Q98*R98,2)</f>
       </c>
       <c r="T98" s="5">
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <f>ROUND(S98*(1-T98),2)</f>
       </c>
       <c r="V98" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W98" s="11">
         <f>IFERROR(VLOOKUP(V98,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X98" s="12">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f>ROUND(U98*W98,2)</f>
       </c>
       <c r="Y98" s="26">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>Q98</f>
       </c>
       <c r="Z98" s="12">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>ROUND(Y98*R98,2)</f>
       </c>
       <c r="AA98" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB98" s="11">
         <f>IFERROR(VLOOKUP(AA98,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC98" s="12">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>ROUND(Y98*AB98*R98,2)</f>
       </c>
       <c r="AD98" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>ROUND(AC98-X98,2)</f>
       </c>
       <c r="AE98" s="13">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>IFERROR(AD98/AC98,0)</f>
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
@@ -7209,53 +6289,43 @@
         <v>0</v>
       </c>
       <c r="S99" s="12">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>ROUND(Q99*R99,2)</f>
       </c>
       <c r="T99" s="5">
         <v>0</v>
       </c>
       <c r="U99" s="12">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>ROUND(S99*(1-T99),2)</f>
       </c>
       <c r="V99" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W99" s="11">
         <f>IFERROR(VLOOKUP(V99,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="X99" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>ROUND(U99*W99,2)</f>
       </c>
       <c r="Y99" s="26">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>Q99</f>
       </c>
       <c r="Z99" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>ROUND(Y99*R99,2)</f>
       </c>
       <c r="AA99" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB99" s="11">
         <f>IFERROR(VLOOKUP(AA99,Curr!$B$2:$C$13,2,FALSE),0)</f>
-        <v>11.3</v>
       </c>
       <c r="AC99" s="12">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>ROUND(Y99*AB99*R99,2)</f>
       </c>
       <c r="AD99" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>ROUND(AC99-X99,2)</f>
       </c>
       <c r="AE99" s="13">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>IFERROR(AD99/AC99,0)</f>
       </c>
     </row>
     <row r="100" spans="2:36" x14ac:dyDescent="0.25">
@@ -7359,41 +6429,32 @@
       </c>
       <c r="Z101" s="15">
         <f>SUM(Z7:Z99)</f>
-        <v>0</v>
       </c>
       <c r="AA101" s="14"/>
       <c r="AB101" s="14"/>
       <c r="AC101" s="15">
         <f>SUM(AC7:AC99)</f>
-        <v>0</v>
       </c>
       <c r="AD101" s="15">
         <f>SUM(AD7:AD99)</f>
-        <v>0</v>
       </c>
       <c r="AE101" s="21">
-        <f t="shared" ref="AE101" si="30">IFERROR(AD101/AC101,0)</f>
-        <v>0</v>
+        <f>IFERROR(AD101/AC101,0)</f>
       </c>
       <c r="AF101" s="15">
-        <f>SUM(AF8:AF100)</f>
-        <v>0</v>
+        <f>SUM(AF7:AF99)</f>
       </c>
       <c r="AG101" s="15">
-        <f>SUM(AG8:AG100)</f>
-        <v>0</v>
+        <f>SUM(AG7:AG99)</f>
       </c>
       <c r="AH101" s="15">
-        <f>SUM(AH8:AH100)</f>
-        <v>0</v>
+        <f>SUM(AH7:AH99)</f>
       </c>
       <c r="AI101" s="15">
-        <f>SUM(AI8:AI100)</f>
-        <v>0</v>
+        <f>SUM(AI7:AI99)</f>
       </c>
       <c r="AJ101" s="15">
-        <f>SUM(AJ8:AJ100)</f>
-        <v>0</v>
+        <f>SUM(AJ7:AJ99)</f>
       </c>
     </row>
     <row r="102" spans="2:36" x14ac:dyDescent="0.25">
@@ -7443,7 +6504,9 @@
       <c r="Y103" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Z103" s="34"/>
+      <c r="Z103" s="34">
+        <f>Z101</f>
+      </c>
       <c r="AA103" s="9"/>
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
@@ -7468,13 +6531,8 @@
       <c r="V104" s="9"/>
       <c r="W104" s="9"/>
       <c r="X104" s="9"/>
-      <c r="Y104" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z104" s="34">
-        <f>Z103/2</f>
-        <v>0</v>
-      </c>
+      <c r="Y104" s="34"/>
+      <c r="Z104" s="34"/>
       <c r="AA104" s="9"/>
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
@@ -7533,7 +6591,6 @@
       </c>
       <c r="Z106" s="9">
         <f>Z103-Z107</f>
-        <v>0</v>
       </c>
       <c r="AA106" s="9"/>
       <c r="AB106" s="9"/>
@@ -7607,7 +6664,6 @@
       </c>
       <c r="Z109" s="9">
         <f>Z103*0.3</f>
-        <v>0</v>
       </c>
       <c r="AA109" s="9"/>
       <c r="AB109" s="9"/>
@@ -7629,7 +6685,6 @@
       </c>
       <c r="Z110" s="9">
         <f>Z107-Z109</f>
-        <v>0</v>
       </c>
       <c r="AA110" s="9"/>
       <c r="AB110" s="9"/>
@@ -7646,7 +6701,6 @@
       </c>
       <c r="Z111" s="9">
         <f>Z103-Z109-Z110</f>
-        <v>0</v>
       </c>
       <c r="AA111" s="9"/>
       <c r="AB111" s="9"/>

--- a/calculator/templates/Calculation-template-Mal.xlsx
+++ b/calculator/templates/Calculation-template-Mal.xlsx
@@ -953,43 +953,53 @@
         <v>0</v>
       </c>
       <c r="S7" s="12">
-        <f>ROUND(Q7*R7,2)</f>
+        <f t="shared" ref="S7" si="0">+Q7*R7</f>
+        <v>0</v>
       </c>
       <c r="T7" s="5">
         <v>0</v>
       </c>
       <c r="U7" s="12">
-        <f>ROUND(S7*(1-T7),2)</f>
+        <f>S7*(1-T7)</f>
+        <v>0</v>
       </c>
       <c r="V7" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W7" s="11">
         <f>IFERROR(VLOOKUP(V7,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X7" s="12">
-        <f>ROUND(U7*W7,2)</f>
+        <f t="shared" ref="X7" si="1">U7*W7</f>
+        <v>0</v>
       </c>
       <c r="Y7" s="26">
         <f>Q7</f>
+        <v>0</v>
       </c>
       <c r="Z7" s="12">
-        <f>ROUND(Y7*R7,2)</f>
+        <f t="shared" ref="Z7" si="2">+Y7*R7</f>
+        <v>0</v>
       </c>
       <c r="AA7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB7" s="11">
         <f>IFERROR(VLOOKUP(AA7,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC7" s="12">
-        <f>ROUND(Y7*AB7*R7,2)</f>
+        <f t="shared" ref="AC7" si="3">+Y7*AB7*R7</f>
+        <v>0</v>
       </c>
       <c r="AD7" s="12">
-        <f>ROUND(AC7-X7,2)</f>
+        <f t="shared" ref="AD7" si="4">+AC7-X7</f>
+        <v>0</v>
       </c>
       <c r="AE7" s="13">
-        <f>IFERROR(AD7/AC7,0)</f>
+        <f t="shared" ref="AE7" si="5">IFERROR(AD7/AC7,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.25">
@@ -1011,43 +1021,53 @@
         <v>0</v>
       </c>
       <c r="S8" s="12">
-        <f>ROUND(Q8*R8,2)</f>
+        <f t="shared" ref="S8:S11" si="6">+Q8*R8</f>
+        <v>0</v>
       </c>
       <c r="T8" s="5">
         <v>0</v>
       </c>
       <c r="U8" s="12">
-        <f>ROUND(S8*(1-T8),2)</f>
+        <f t="shared" ref="U8:U11" si="7">S8*(1-T8)</f>
+        <v>0</v>
       </c>
       <c r="V8" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W8" s="11">
         <f>IFERROR(VLOOKUP(V8,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X8" s="12">
-        <f>ROUND(U8*W8,2)</f>
+        <f t="shared" ref="X8:X11" si="8">U8*W8</f>
+        <v>0</v>
       </c>
       <c r="Y8" s="26">
-        <f>Q8</f>
+        <f t="shared" ref="Y8:Y11" si="9">Q8</f>
+        <v>0</v>
       </c>
       <c r="Z8" s="12">
-        <f>ROUND(Y8*R8,2)</f>
+        <f t="shared" ref="Z8:Z11" si="10">+Y8*R8</f>
+        <v>0</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB8" s="11">
         <f>IFERROR(VLOOKUP(AA8,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC8" s="12">
-        <f>ROUND(Y8*AB8*R8,2)</f>
+        <f t="shared" ref="AC8:AC11" si="11">+Y8*AB8*R8</f>
+        <v>0</v>
       </c>
       <c r="AD8" s="12">
-        <f>ROUND(AC8-X8,2)</f>
+        <f t="shared" ref="AD8:AD11" si="12">+AC8-X8</f>
+        <v>0</v>
       </c>
       <c r="AE8" s="13">
-        <f>IFERROR(AD8/AC8,0)</f>
+        <f t="shared" ref="AE8:AE11" si="13">IFERROR(AD8/AC8,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.25">
@@ -1069,43 +1089,53 @@
         <v>0</v>
       </c>
       <c r="S9" s="12">
-        <f>ROUND(Q9*R9,2)</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="T9" s="5">
         <v>0</v>
       </c>
       <c r="U9" s="12">
-        <f>ROUND(S9*(1-T9),2)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="V9" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W9" s="11">
         <f>IFERROR(VLOOKUP(V9,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X9" s="12">
-        <f>ROUND(U9*W9,2)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="Y9" s="26">
-        <f>Q9</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="Z9" s="12">
-        <f>ROUND(Y9*R9,2)</f>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB9" s="11">
         <f>IFERROR(VLOOKUP(AA9,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC9" s="12">
-        <f>ROUND(Y9*AB9*R9,2)</f>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="AD9" s="12">
-        <f>ROUND(AC9-X9,2)</f>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="AE9" s="13">
-        <f>IFERROR(AD9/AC9,0)</f>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.25">
@@ -1127,43 +1157,53 @@
         <v>0</v>
       </c>
       <c r="S10" s="12">
-        <f>ROUND(Q10*R10,2)</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="T10" s="5">
         <v>0</v>
       </c>
       <c r="U10" s="12">
-        <f>ROUND(S10*(1-T10),2)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="V10" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W10" s="11">
         <f>IFERROR(VLOOKUP(V10,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X10" s="12">
-        <f>ROUND(U10*W10,2)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="Y10" s="26">
-        <f>Q10</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="Z10" s="12">
-        <f>ROUND(Y10*R10,2)</f>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="AA10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB10" s="11">
         <f>IFERROR(VLOOKUP(AA10,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC10" s="12">
-        <f>ROUND(Y10*AB10*R10,2)</f>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="AD10" s="12">
-        <f>ROUND(AC10-X10,2)</f>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="AE10" s="13">
-        <f>IFERROR(AD10/AC10,0)</f>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.25">
@@ -1185,43 +1225,53 @@
         <v>0</v>
       </c>
       <c r="S11" s="12">
-        <f>ROUND(Q11*R11,2)</f>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="T11" s="5">
         <v>0</v>
       </c>
       <c r="U11" s="12">
-        <f>ROUND(S11*(1-T11),2)</f>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="V11" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W11" s="11">
         <f>IFERROR(VLOOKUP(V11,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X11" s="12">
-        <f>ROUND(U11*W11,2)</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="Y11" s="26">
-        <f>Q11</f>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="Z11" s="12">
-        <f>ROUND(Y11*R11,2)</f>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB11" s="11">
         <f>IFERROR(VLOOKUP(AA11,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC11" s="12">
-        <f>ROUND(Y11*AB11*R11,2)</f>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="AD11" s="12">
-        <f>ROUND(AC11-X11,2)</f>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
       <c r="AE11" s="13">
-        <f>IFERROR(AD11/AC11,0)</f>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.25">
@@ -1243,43 +1293,53 @@
         <v>0</v>
       </c>
       <c r="S12" s="12">
-        <f>ROUND(Q12*R12,2)</f>
+        <f t="shared" ref="S12:S99" si="14">+Q12*R12</f>
+        <v>0</v>
       </c>
       <c r="T12" s="5">
         <v>0</v>
       </c>
       <c r="U12" s="12">
-        <f>ROUND(S12*(1-T12),2)</f>
+        <f t="shared" ref="U12:U99" si="15">S12*(1-T12)</f>
+        <v>0</v>
       </c>
       <c r="V12" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W12" s="11">
         <f>IFERROR(VLOOKUP(V12,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X12" s="12">
-        <f>ROUND(U12*W12,2)</f>
+        <f t="shared" ref="X12:X99" si="16">U12*W12</f>
+        <v>0</v>
       </c>
       <c r="Y12" s="26">
-        <f>Q12</f>
+        <f t="shared" ref="Y12:Y99" si="17">Q12</f>
+        <v>0</v>
       </c>
       <c r="Z12" s="12">
-        <f>ROUND(Y12*R12,2)</f>
+        <f t="shared" ref="Z12:Z99" si="18">+Y12*R12</f>
+        <v>0</v>
       </c>
       <c r="AA12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB12" s="11">
         <f>IFERROR(VLOOKUP(AA12,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC12" s="12">
-        <f>ROUND(Y12*AB12*R12,2)</f>
+        <f t="shared" ref="AC12:AC99" si="19">+Y12*AB12*R12</f>
+        <v>0</v>
       </c>
       <c r="AD12" s="12">
-        <f>ROUND(AC12-X12,2)</f>
+        <f t="shared" ref="AD12:AD99" si="20">+AC12-X12</f>
+        <v>0</v>
       </c>
       <c r="AE12" s="13">
-        <f>IFERROR(AD12/AC12,0)</f>
+        <f t="shared" ref="AE12:AE99" si="21">IFERROR(AD12/AC12,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.25">
@@ -1301,43 +1361,53 @@
         <v>0</v>
       </c>
       <c r="S13" s="12">
-        <f>ROUND(Q13*R13,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T13" s="5">
         <v>0</v>
       </c>
       <c r="U13" s="12">
-        <f>ROUND(S13*(1-T13),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V13" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W13" s="11">
         <f>IFERROR(VLOOKUP(V13,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X13" s="12">
-        <f>ROUND(U13*W13,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y13" s="26">
-        <f>Q13</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z13" s="12">
-        <f>ROUND(Y13*R13,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB13" s="11">
         <f>IFERROR(VLOOKUP(AA13,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC13" s="12">
-        <f>ROUND(Y13*AB13*R13,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD13" s="12">
-        <f>ROUND(AC13-X13,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE13" s="13">
-        <f>IFERROR(AD13/AC13,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.25">
@@ -1359,43 +1429,53 @@
         <v>0</v>
       </c>
       <c r="S14" s="12">
-        <f>ROUND(Q14*R14,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T14" s="5">
         <v>0</v>
       </c>
       <c r="U14" s="12">
-        <f>ROUND(S14*(1-T14),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V14" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W14" s="11">
         <f>IFERROR(VLOOKUP(V14,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X14" s="12">
-        <f>ROUND(U14*W14,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y14" s="26">
-        <f>Q14</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z14" s="12">
-        <f>ROUND(Y14*R14,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB14" s="11">
         <f>IFERROR(VLOOKUP(AA14,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC14" s="12">
-        <f>ROUND(Y14*AB14*R14,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD14" s="12">
-        <f>ROUND(AC14-X14,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE14" s="13">
-        <f>IFERROR(AD14/AC14,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.25">
@@ -1417,43 +1497,53 @@
         <v>0</v>
       </c>
       <c r="S15" s="12">
-        <f>ROUND(Q15*R15,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T15" s="5">
         <v>0</v>
       </c>
       <c r="U15" s="12">
-        <f>ROUND(S15*(1-T15),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V15" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W15" s="11">
         <f>IFERROR(VLOOKUP(V15,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X15" s="12">
-        <f>ROUND(U15*W15,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y15" s="26">
-        <f>Q15</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z15" s="12">
-        <f>ROUND(Y15*R15,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB15" s="11">
         <f>IFERROR(VLOOKUP(AA15,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC15" s="12">
-        <f>ROUND(Y15*AB15*R15,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD15" s="12">
-        <f>ROUND(AC15-X15,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE15" s="13">
-        <f>IFERROR(AD15/AC15,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.25">
@@ -1475,43 +1565,53 @@
         <v>0</v>
       </c>
       <c r="S16" s="12">
-        <f>ROUND(Q16*R16,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T16" s="5">
         <v>0</v>
       </c>
       <c r="U16" s="12">
-        <f>ROUND(S16*(1-T16),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V16" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W16" s="11">
         <f>IFERROR(VLOOKUP(V16,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X16" s="12">
-        <f>ROUND(U16*W16,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y16" s="26">
-        <f>Q16</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z16" s="12">
-        <f>ROUND(Y16*R16,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB16" s="11">
         <f>IFERROR(VLOOKUP(AA16,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC16" s="12">
-        <f>ROUND(Y16*AB16*R16,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD16" s="12">
-        <f>ROUND(AC16-X16,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE16" s="13">
-        <f>IFERROR(AD16/AC16,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.25">
@@ -1533,43 +1633,53 @@
         <v>0</v>
       </c>
       <c r="S17" s="12">
-        <f>ROUND(Q17*R17,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
       </c>
       <c r="U17" s="12">
-        <f>ROUND(S17*(1-T17),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W17" s="11">
         <f>IFERROR(VLOOKUP(V17,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X17" s="12">
-        <f>ROUND(U17*W17,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y17" s="26">
-        <f>Q17</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z17" s="12">
-        <f>ROUND(Y17*R17,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB17" s="11">
         <f>IFERROR(VLOOKUP(AA17,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC17" s="12">
-        <f>ROUND(Y17*AB17*R17,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD17" s="12">
-        <f>ROUND(AC17-X17,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE17" s="13">
-        <f>IFERROR(AD17/AC17,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.25">
@@ -1591,43 +1701,53 @@
         <v>0</v>
       </c>
       <c r="S18" s="12">
-        <f>ROUND(Q18*R18,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T18" s="5">
         <v>0</v>
       </c>
       <c r="U18" s="12">
-        <f>ROUND(S18*(1-T18),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V18" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W18" s="11">
         <f>IFERROR(VLOOKUP(V18,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X18" s="12">
-        <f>ROUND(U18*W18,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y18" s="26">
-        <f>Q18</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z18" s="12">
-        <f>ROUND(Y18*R18,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB18" s="11">
         <f>IFERROR(VLOOKUP(AA18,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC18" s="12">
-        <f>ROUND(Y18*AB18*R18,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD18" s="12">
-        <f>ROUND(AC18-X18,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE18" s="13">
-        <f>IFERROR(AD18/AC18,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
@@ -1649,43 +1769,53 @@
         <v>0</v>
       </c>
       <c r="S19" s="12">
-        <f>ROUND(Q19*R19,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T19" s="5">
         <v>0</v>
       </c>
       <c r="U19" s="12">
-        <f>ROUND(S19*(1-T19),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V19" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W19" s="11">
         <f>IFERROR(VLOOKUP(V19,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X19" s="12">
-        <f>ROUND(U19*W19,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y19" s="26">
-        <f>Q19</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z19" s="12">
-        <f>ROUND(Y19*R19,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB19" s="11">
         <f>IFERROR(VLOOKUP(AA19,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC19" s="12">
-        <f>ROUND(Y19*AB19*R19,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD19" s="12">
-        <f>ROUND(AC19-X19,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE19" s="13">
-        <f>IFERROR(AD19/AC19,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
@@ -1707,43 +1837,53 @@
         <v>0</v>
       </c>
       <c r="S20" s="12">
-        <f>ROUND(Q20*R20,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T20" s="5">
         <v>0</v>
       </c>
       <c r="U20" s="12">
-        <f>ROUND(S20*(1-T20),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V20" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W20" s="11">
         <f>IFERROR(VLOOKUP(V20,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X20" s="12">
-        <f>ROUND(U20*W20,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y20" s="26">
-        <f>Q20</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <f>ROUND(Y20*R20,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB20" s="11">
         <f>IFERROR(VLOOKUP(AA20,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC20" s="12">
-        <f>ROUND(Y20*AB20*R20,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD20" s="12">
-        <f>ROUND(AC20-X20,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE20" s="13">
-        <f>IFERROR(AD20/AC20,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:31" x14ac:dyDescent="0.25">
@@ -1765,43 +1905,53 @@
         <v>0</v>
       </c>
       <c r="S21" s="12">
-        <f>ROUND(Q21*R21,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T21" s="5">
         <v>0</v>
       </c>
       <c r="U21" s="12">
-        <f>ROUND(S21*(1-T21),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V21" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W21" s="11">
         <f>IFERROR(VLOOKUP(V21,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X21" s="12">
-        <f>ROUND(U21*W21,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y21" s="26">
-        <f>Q21</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z21" s="12">
-        <f>ROUND(Y21*R21,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB21" s="11">
         <f>IFERROR(VLOOKUP(AA21,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC21" s="12">
-        <f>ROUND(Y21*AB21*R21,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD21" s="12">
-        <f>ROUND(AC21-X21,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE21" s="13">
-        <f>IFERROR(AD21/AC21,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.25">
@@ -1823,43 +1973,53 @@
         <v>0</v>
       </c>
       <c r="S22" s="12">
-        <f>ROUND(Q22*R22,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T22" s="5">
         <v>0</v>
       </c>
       <c r="U22" s="12">
-        <f>ROUND(S22*(1-T22),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V22" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W22" s="11">
         <f>IFERROR(VLOOKUP(V22,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X22" s="12">
-        <f>ROUND(U22*W22,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y22" s="26">
-        <f>Q22</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z22" s="12">
-        <f>ROUND(Y22*R22,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB22" s="11">
         <f>IFERROR(VLOOKUP(AA22,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC22" s="12">
-        <f>ROUND(Y22*AB22*R22,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD22" s="12">
-        <f>ROUND(AC22-X22,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE22" s="13">
-        <f>IFERROR(AD22/AC22,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.25">
@@ -1881,43 +2041,53 @@
         <v>0</v>
       </c>
       <c r="S23" s="12">
-        <f>ROUND(Q23*R23,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T23" s="5">
         <v>0</v>
       </c>
       <c r="U23" s="12">
-        <f>ROUND(S23*(1-T23),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V23" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W23" s="11">
         <f>IFERROR(VLOOKUP(V23,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X23" s="12">
-        <f>ROUND(U23*W23,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y23" s="26">
-        <f>Q23</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z23" s="12">
-        <f>ROUND(Y23*R23,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB23" s="11">
         <f>IFERROR(VLOOKUP(AA23,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC23" s="12">
-        <f>ROUND(Y23*AB23*R23,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD23" s="12">
-        <f>ROUND(AC23-X23,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE23" s="13">
-        <f>IFERROR(AD23/AC23,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.25">
@@ -1939,43 +2109,53 @@
         <v>0</v>
       </c>
       <c r="S24" s="12">
-        <f>ROUND(Q24*R24,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T24" s="5">
         <v>0</v>
       </c>
       <c r="U24" s="12">
-        <f>ROUND(S24*(1-T24),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V24" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W24" s="11">
         <f>IFERROR(VLOOKUP(V24,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X24" s="12">
-        <f>ROUND(U24*W24,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y24" s="26">
-        <f>Q24</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z24" s="12">
-        <f>ROUND(Y24*R24,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB24" s="11">
         <f>IFERROR(VLOOKUP(AA24,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC24" s="12">
-        <f>ROUND(Y24*AB24*R24,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD24" s="12">
-        <f>ROUND(AC24-X24,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE24" s="13">
-        <f>IFERROR(AD24/AC24,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.25">
@@ -1997,43 +2177,53 @@
         <v>0</v>
       </c>
       <c r="S25" s="12">
-        <f>ROUND(Q25*R25,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T25" s="5">
         <v>0</v>
       </c>
       <c r="U25" s="12">
-        <f>ROUND(S25*(1-T25),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V25" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W25" s="11">
         <f>IFERROR(VLOOKUP(V25,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X25" s="12">
-        <f>ROUND(U25*W25,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y25" s="26">
-        <f>Q25</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z25" s="12">
-        <f>ROUND(Y25*R25,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB25" s="11">
         <f>IFERROR(VLOOKUP(AA25,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC25" s="12">
-        <f>ROUND(Y25*AB25*R25,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD25" s="12">
-        <f>ROUND(AC25-X25,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE25" s="13">
-        <f>IFERROR(AD25/AC25,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:31" x14ac:dyDescent="0.25">
@@ -2055,43 +2245,53 @@
         <v>0</v>
       </c>
       <c r="S26" s="12">
-        <f>ROUND(Q26*R26,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T26" s="5">
         <v>0</v>
       </c>
       <c r="U26" s="12">
-        <f>ROUND(S26*(1-T26),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V26" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W26" s="11">
         <f>IFERROR(VLOOKUP(V26,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X26" s="12">
-        <f>ROUND(U26*W26,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y26" s="26">
-        <f>Q26</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z26" s="12">
-        <f>ROUND(Y26*R26,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB26" s="11">
         <f>IFERROR(VLOOKUP(AA26,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC26" s="12">
-        <f>ROUND(Y26*AB26*R26,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD26" s="12">
-        <f>ROUND(AC26-X26,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE26" s="13">
-        <f>IFERROR(AD26/AC26,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:31" x14ac:dyDescent="0.25">
@@ -2113,43 +2313,53 @@
         <v>0</v>
       </c>
       <c r="S27" s="12">
-        <f>ROUND(Q27*R27,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T27" s="5">
         <v>0</v>
       </c>
       <c r="U27" s="12">
-        <f>ROUND(S27*(1-T27),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V27" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W27" s="11">
         <f>IFERROR(VLOOKUP(V27,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X27" s="12">
-        <f>ROUND(U27*W27,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y27" s="26">
-        <f>Q27</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z27" s="12">
-        <f>ROUND(Y27*R27,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB27" s="11">
         <f>IFERROR(VLOOKUP(AA27,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC27" s="12">
-        <f>ROUND(Y27*AB27*R27,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD27" s="12">
-        <f>ROUND(AC27-X27,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE27" s="13">
-        <f>IFERROR(AD27/AC27,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.25">
@@ -2171,43 +2381,53 @@
         <v>0</v>
       </c>
       <c r="S28" s="12">
-        <f>ROUND(Q28*R28,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T28" s="5">
         <v>0</v>
       </c>
       <c r="U28" s="12">
-        <f>ROUND(S28*(1-T28),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V28" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W28" s="11">
         <f>IFERROR(VLOOKUP(V28,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X28" s="12">
-        <f>ROUND(U28*W28,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y28" s="26">
-        <f>Q28</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z28" s="12">
-        <f>ROUND(Y28*R28,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB28" s="11">
         <f>IFERROR(VLOOKUP(AA28,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC28" s="12">
-        <f>ROUND(Y28*AB28*R28,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD28" s="12">
-        <f>ROUND(AC28-X28,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(AD28/AC28,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.25">
@@ -2229,43 +2449,53 @@
         <v>0</v>
       </c>
       <c r="S29" s="12">
-        <f>ROUND(Q29*R29,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T29" s="5">
         <v>0</v>
       </c>
       <c r="U29" s="12">
-        <f>ROUND(S29*(1-T29),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V29" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W29" s="11">
         <f>IFERROR(VLOOKUP(V29,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X29" s="12">
-        <f>ROUND(U29*W29,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y29" s="26">
-        <f>Q29</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z29" s="12">
-        <f>ROUND(Y29*R29,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB29" s="11">
         <f>IFERROR(VLOOKUP(AA29,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC29" s="12">
-        <f>ROUND(Y29*AB29*R29,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD29" s="12">
-        <f>ROUND(AC29-X29,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE29" s="13">
-        <f>IFERROR(AD29/AC29,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.25">
@@ -2287,43 +2517,53 @@
         <v>0</v>
       </c>
       <c r="S30" s="12">
-        <f>ROUND(Q30*R30,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T30" s="5">
         <v>0</v>
       </c>
       <c r="U30" s="12">
-        <f>ROUND(S30*(1-T30),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V30" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W30" s="11">
         <f>IFERROR(VLOOKUP(V30,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X30" s="12">
-        <f>ROUND(U30*W30,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y30" s="26">
-        <f>Q30</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z30" s="12">
-        <f>ROUND(Y30*R30,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB30" s="11">
         <f>IFERROR(VLOOKUP(AA30,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC30" s="12">
-        <f>ROUND(Y30*AB30*R30,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD30" s="12">
-        <f>ROUND(AC30-X30,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE30" s="13">
-        <f>IFERROR(AD30/AC30,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:31" x14ac:dyDescent="0.25">
@@ -2345,43 +2585,53 @@
         <v>0</v>
       </c>
       <c r="S31" s="12">
-        <f>ROUND(Q31*R31,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T31" s="5">
         <v>0</v>
       </c>
       <c r="U31" s="12">
-        <f>ROUND(S31*(1-T31),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V31" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W31" s="11">
         <f>IFERROR(VLOOKUP(V31,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X31" s="12">
-        <f>ROUND(U31*W31,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y31" s="26">
-        <f>Q31</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z31" s="12">
-        <f>ROUND(Y31*R31,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA31" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB31" s="11">
         <f>IFERROR(VLOOKUP(AA31,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC31" s="12">
-        <f>ROUND(Y31*AB31*R31,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD31" s="12">
-        <f>ROUND(AC31-X31,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(AD31/AC31,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.25">
@@ -2403,43 +2653,53 @@
         <v>0</v>
       </c>
       <c r="S32" s="12">
-        <f>ROUND(Q32*R32,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T32" s="5">
         <v>0</v>
       </c>
       <c r="U32" s="12">
-        <f>ROUND(S32*(1-T32),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V32" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W32" s="11">
         <f>IFERROR(VLOOKUP(V32,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X32" s="12">
-        <f>ROUND(U32*W32,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y32" s="26">
-        <f>Q32</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z32" s="12">
-        <f>ROUND(Y32*R32,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB32" s="11">
         <f>IFERROR(VLOOKUP(AA32,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC32" s="12">
-        <f>ROUND(Y32*AB32*R32,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD32" s="12">
-        <f>ROUND(AC32-X32,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE32" s="13">
-        <f>IFERROR(AD32/AC32,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:31" x14ac:dyDescent="0.25">
@@ -2461,43 +2721,53 @@
         <v>0</v>
       </c>
       <c r="S33" s="12">
-        <f>ROUND(Q33*R33,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T33" s="5">
         <v>0</v>
       </c>
       <c r="U33" s="12">
-        <f>ROUND(S33*(1-T33),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V33" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W33" s="11">
         <f>IFERROR(VLOOKUP(V33,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X33" s="12">
-        <f>ROUND(U33*W33,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y33" s="26">
-        <f>Q33</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z33" s="12">
-        <f>ROUND(Y33*R33,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB33" s="11">
         <f>IFERROR(VLOOKUP(AA33,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC33" s="12">
-        <f>ROUND(Y33*AB33*R33,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD33" s="12">
-        <f>ROUND(AC33-X33,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE33" s="13">
-        <f>IFERROR(AD33/AC33,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:31" x14ac:dyDescent="0.25">
@@ -2519,43 +2789,53 @@
         <v>0</v>
       </c>
       <c r="S34" s="12">
-        <f>ROUND(Q34*R34,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T34" s="5">
         <v>0</v>
       </c>
       <c r="U34" s="12">
-        <f>ROUND(S34*(1-T34),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V34" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W34" s="11">
         <f>IFERROR(VLOOKUP(V34,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X34" s="12">
-        <f>ROUND(U34*W34,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y34" s="26">
-        <f>Q34</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z34" s="12">
-        <f>ROUND(Y34*R34,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB34" s="11">
         <f>IFERROR(VLOOKUP(AA34,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC34" s="12">
-        <f>ROUND(Y34*AB34*R34,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD34" s="12">
-        <f>ROUND(AC34-X34,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE34" s="13">
-        <f>IFERROR(AD34/AC34,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:31" x14ac:dyDescent="0.25">
@@ -2577,43 +2857,53 @@
         <v>0</v>
       </c>
       <c r="S35" s="12">
-        <f>ROUND(Q35*R35,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T35" s="5">
         <v>0</v>
       </c>
       <c r="U35" s="12">
-        <f>ROUND(S35*(1-T35),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V35" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W35" s="11">
         <f>IFERROR(VLOOKUP(V35,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X35" s="12">
-        <f>ROUND(U35*W35,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y35" s="26">
-        <f>Q35</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z35" s="12">
-        <f>ROUND(Y35*R35,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB35" s="11">
         <f>IFERROR(VLOOKUP(AA35,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC35" s="12">
-        <f>ROUND(Y35*AB35*R35,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD35" s="12">
-        <f>ROUND(AC35-X35,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE35" s="13">
-        <f>IFERROR(AD35/AC35,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:31" x14ac:dyDescent="0.25">
@@ -2635,43 +2925,53 @@
         <v>0</v>
       </c>
       <c r="S36" s="12">
-        <f>ROUND(Q36*R36,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T36" s="5">
         <v>0</v>
       </c>
       <c r="U36" s="12">
-        <f>ROUND(S36*(1-T36),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V36" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W36" s="11">
         <f>IFERROR(VLOOKUP(V36,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X36" s="12">
-        <f>ROUND(U36*W36,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y36" s="26">
-        <f>Q36</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z36" s="12">
-        <f>ROUND(Y36*R36,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB36" s="11">
         <f>IFERROR(VLOOKUP(AA36,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC36" s="12">
-        <f>ROUND(Y36*AB36*R36,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD36" s="12">
-        <f>ROUND(AC36-X36,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE36" s="13">
-        <f>IFERROR(AD36/AC36,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:31" x14ac:dyDescent="0.25">
@@ -2693,43 +2993,53 @@
         <v>0</v>
       </c>
       <c r="S37" s="12">
-        <f>ROUND(Q37*R37,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T37" s="5">
         <v>0</v>
       </c>
       <c r="U37" s="12">
-        <f>ROUND(S37*(1-T37),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V37" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W37" s="11">
         <f>IFERROR(VLOOKUP(V37,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X37" s="12">
-        <f>ROUND(U37*W37,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y37" s="26">
-        <f>Q37</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z37" s="12">
-        <f>ROUND(Y37*R37,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB37" s="11">
         <f>IFERROR(VLOOKUP(AA37,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC37" s="12">
-        <f>ROUND(Y37*AB37*R37,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD37" s="12">
-        <f>ROUND(AC37-X37,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE37" s="13">
-        <f>IFERROR(AD37/AC37,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:31" x14ac:dyDescent="0.25">
@@ -2751,43 +3061,53 @@
         <v>0</v>
       </c>
       <c r="S38" s="12">
-        <f>ROUND(Q38*R38,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T38" s="5">
         <v>0</v>
       </c>
       <c r="U38" s="12">
-        <f>ROUND(S38*(1-T38),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V38" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W38" s="11">
         <f>IFERROR(VLOOKUP(V38,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X38" s="12">
-        <f>ROUND(U38*W38,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y38" s="26">
-        <f>Q38</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z38" s="12">
-        <f>ROUND(Y38*R38,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB38" s="11">
         <f>IFERROR(VLOOKUP(AA38,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC38" s="12">
-        <f>ROUND(Y38*AB38*R38,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD38" s="12">
-        <f>ROUND(AC38-X38,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE38" s="13">
-        <f>IFERROR(AD38/AC38,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:31" x14ac:dyDescent="0.25">
@@ -2809,43 +3129,53 @@
         <v>0</v>
       </c>
       <c r="S39" s="12">
-        <f>ROUND(Q39*R39,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T39" s="5">
         <v>0</v>
       </c>
       <c r="U39" s="12">
-        <f>ROUND(S39*(1-T39),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V39" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W39" s="11">
         <f>IFERROR(VLOOKUP(V39,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X39" s="12">
-        <f>ROUND(U39*W39,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y39" s="26">
-        <f>Q39</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z39" s="12">
-        <f>ROUND(Y39*R39,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB39" s="11">
         <f>IFERROR(VLOOKUP(AA39,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC39" s="12">
-        <f>ROUND(Y39*AB39*R39,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD39" s="12">
-        <f>ROUND(AC39-X39,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE39" s="13">
-        <f>IFERROR(AD39/AC39,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:31" x14ac:dyDescent="0.25">
@@ -2867,43 +3197,53 @@
         <v>0</v>
       </c>
       <c r="S40" s="12">
-        <f>ROUND(Q40*R40,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T40" s="5">
         <v>0</v>
       </c>
       <c r="U40" s="12">
-        <f>ROUND(S40*(1-T40),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V40" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W40" s="11">
         <f>IFERROR(VLOOKUP(V40,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X40" s="12">
-        <f>ROUND(U40*W40,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y40" s="26">
-        <f>Q40</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z40" s="12">
-        <f>ROUND(Y40*R40,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB40" s="11">
         <f>IFERROR(VLOOKUP(AA40,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC40" s="12">
-        <f>ROUND(Y40*AB40*R40,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD40" s="12">
-        <f>ROUND(AC40-X40,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE40" s="13">
-        <f>IFERROR(AD40/AC40,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.25">
@@ -2925,43 +3265,53 @@
         <v>0</v>
       </c>
       <c r="S41" s="12">
-        <f>ROUND(Q41*R41,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T41" s="5">
         <v>0</v>
       </c>
       <c r="U41" s="12">
-        <f>ROUND(S41*(1-T41),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V41" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W41" s="11">
         <f>IFERROR(VLOOKUP(V41,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X41" s="12">
-        <f>ROUND(U41*W41,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y41" s="26">
-        <f>Q41</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z41" s="12">
-        <f>ROUND(Y41*R41,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA41" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB41" s="11">
         <f>IFERROR(VLOOKUP(AA41,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC41" s="12">
-        <f>ROUND(Y41*AB41*R41,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD41" s="12">
-        <f>ROUND(AC41-X41,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE41" s="13">
-        <f>IFERROR(AD41/AC41,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:31" x14ac:dyDescent="0.25">
@@ -2983,43 +3333,53 @@
         <v>0</v>
       </c>
       <c r="S42" s="12">
-        <f>ROUND(Q42*R42,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T42" s="5">
         <v>0</v>
       </c>
       <c r="U42" s="12">
-        <f>ROUND(S42*(1-T42),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V42" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W42" s="11">
         <f>IFERROR(VLOOKUP(V42,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X42" s="12">
-        <f>ROUND(U42*W42,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y42" s="26">
-        <f>Q42</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z42" s="12">
-        <f>ROUND(Y42*R42,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB42" s="11">
         <f>IFERROR(VLOOKUP(AA42,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC42" s="12">
-        <f>ROUND(Y42*AB42*R42,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD42" s="12">
-        <f>ROUND(AC42-X42,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE42" s="13">
-        <f>IFERROR(AD42/AC42,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.25">
@@ -3041,43 +3401,53 @@
         <v>0</v>
       </c>
       <c r="S43" s="12">
-        <f>ROUND(Q43*R43,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T43" s="5">
         <v>0</v>
       </c>
       <c r="U43" s="12">
-        <f>ROUND(S43*(1-T43),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V43" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W43" s="11">
         <f>IFERROR(VLOOKUP(V43,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X43" s="12">
-        <f>ROUND(U43*W43,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y43" s="26">
-        <f>Q43</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z43" s="12">
-        <f>ROUND(Y43*R43,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB43" s="11">
         <f>IFERROR(VLOOKUP(AA43,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC43" s="12">
-        <f>ROUND(Y43*AB43*R43,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD43" s="12">
-        <f>ROUND(AC43-X43,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE43" s="13">
-        <f>IFERROR(AD43/AC43,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:31" x14ac:dyDescent="0.25">
@@ -3099,43 +3469,53 @@
         <v>0</v>
       </c>
       <c r="S44" s="12">
-        <f>ROUND(Q44*R44,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T44" s="5">
         <v>0</v>
       </c>
       <c r="U44" s="12">
-        <f>ROUND(S44*(1-T44),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V44" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W44" s="11">
         <f>IFERROR(VLOOKUP(V44,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X44" s="12">
-        <f>ROUND(U44*W44,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y44" s="26">
-        <f>Q44</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z44" s="12">
-        <f>ROUND(Y44*R44,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB44" s="11">
         <f>IFERROR(VLOOKUP(AA44,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC44" s="12">
-        <f>ROUND(Y44*AB44*R44,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD44" s="12">
-        <f>ROUND(AC44-X44,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE44" s="13">
-        <f>IFERROR(AD44/AC44,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:31" x14ac:dyDescent="0.25">
@@ -3157,43 +3537,53 @@
         <v>0</v>
       </c>
       <c r="S45" s="12">
-        <f>ROUND(Q45*R45,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T45" s="5">
         <v>0</v>
       </c>
       <c r="U45" s="12">
-        <f>ROUND(S45*(1-T45),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V45" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W45" s="11">
         <f>IFERROR(VLOOKUP(V45,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X45" s="12">
-        <f>ROUND(U45*W45,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y45" s="26">
-        <f>Q45</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z45" s="12">
-        <f>ROUND(Y45*R45,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA45" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB45" s="11">
         <f>IFERROR(VLOOKUP(AA45,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC45" s="12">
-        <f>ROUND(Y45*AB45*R45,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD45" s="12">
-        <f>ROUND(AC45-X45,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE45" s="13">
-        <f>IFERROR(AD45/AC45,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:31" x14ac:dyDescent="0.25">
@@ -3215,43 +3605,53 @@
         <v>0</v>
       </c>
       <c r="S46" s="12">
-        <f>ROUND(Q46*R46,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T46" s="5">
         <v>0</v>
       </c>
       <c r="U46" s="12">
-        <f>ROUND(S46*(1-T46),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V46" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W46" s="11">
         <f>IFERROR(VLOOKUP(V46,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X46" s="12">
-        <f>ROUND(U46*W46,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y46" s="26">
-        <f>Q46</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z46" s="12">
-        <f>ROUND(Y46*R46,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA46" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB46" s="11">
         <f>IFERROR(VLOOKUP(AA46,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC46" s="12">
-        <f>ROUND(Y46*AB46*R46,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD46" s="12">
-        <f>ROUND(AC46-X46,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE46" s="13">
-        <f>IFERROR(AD46/AC46,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:31" x14ac:dyDescent="0.25">
@@ -3273,43 +3673,53 @@
         <v>0</v>
       </c>
       <c r="S47" s="12">
-        <f>ROUND(Q47*R47,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T47" s="5">
         <v>0</v>
       </c>
       <c r="U47" s="12">
-        <f>ROUND(S47*(1-T47),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V47" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W47" s="11">
         <f>IFERROR(VLOOKUP(V47,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X47" s="12">
-        <f>ROUND(U47*W47,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y47" s="26">
-        <f>Q47</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z47" s="12">
-        <f>ROUND(Y47*R47,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA47" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB47" s="11">
         <f>IFERROR(VLOOKUP(AA47,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC47" s="12">
-        <f>ROUND(Y47*AB47*R47,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD47" s="12">
-        <f>ROUND(AC47-X47,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE47" s="13">
-        <f>IFERROR(AD47/AC47,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:31" x14ac:dyDescent="0.25">
@@ -3331,43 +3741,53 @@
         <v>0</v>
       </c>
       <c r="S48" s="12">
-        <f>ROUND(Q48*R48,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T48" s="5">
         <v>0</v>
       </c>
       <c r="U48" s="12">
-        <f>ROUND(S48*(1-T48),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V48" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W48" s="11">
         <f>IFERROR(VLOOKUP(V48,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X48" s="12">
-        <f>ROUND(U48*W48,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y48" s="26">
-        <f>Q48</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z48" s="12">
-        <f>ROUND(Y48*R48,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA48" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB48" s="11">
         <f>IFERROR(VLOOKUP(AA48,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC48" s="12">
-        <f>ROUND(Y48*AB48*R48,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD48" s="12">
-        <f>ROUND(AC48-X48,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE48" s="13">
-        <f>IFERROR(AD48/AC48,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:31" x14ac:dyDescent="0.25">
@@ -3389,43 +3809,53 @@
         <v>0</v>
       </c>
       <c r="S49" s="12">
-        <f>ROUND(Q49*R49,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T49" s="5">
         <v>0</v>
       </c>
       <c r="U49" s="12">
-        <f>ROUND(S49*(1-T49),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V49" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W49" s="11">
         <f>IFERROR(VLOOKUP(V49,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X49" s="12">
-        <f>ROUND(U49*W49,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y49" s="26">
-        <f>Q49</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z49" s="12">
-        <f>ROUND(Y49*R49,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA49" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB49" s="11">
         <f>IFERROR(VLOOKUP(AA49,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC49" s="12">
-        <f>ROUND(Y49*AB49*R49,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD49" s="12">
-        <f>ROUND(AC49-X49,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE49" s="13">
-        <f>IFERROR(AD49/AC49,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:31" x14ac:dyDescent="0.25">
@@ -3447,43 +3877,53 @@
         <v>0</v>
       </c>
       <c r="S50" s="12">
-        <f>ROUND(Q50*R50,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T50" s="5">
         <v>0</v>
       </c>
       <c r="U50" s="12">
-        <f>ROUND(S50*(1-T50),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V50" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W50" s="11">
         <f>IFERROR(VLOOKUP(V50,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X50" s="12">
-        <f>ROUND(U50*W50,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y50" s="26">
-        <f>Q50</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z50" s="12">
-        <f>ROUND(Y50*R50,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA50" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB50" s="11">
         <f>IFERROR(VLOOKUP(AA50,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC50" s="12">
-        <f>ROUND(Y50*AB50*R50,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD50" s="12">
-        <f>ROUND(AC50-X50,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE50" s="13">
-        <f>IFERROR(AD50/AC50,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:31" x14ac:dyDescent="0.25">
@@ -3505,43 +3945,53 @@
         <v>0</v>
       </c>
       <c r="S51" s="12">
-        <f>ROUND(Q51*R51,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T51" s="5">
         <v>0</v>
       </c>
       <c r="U51" s="12">
-        <f>ROUND(S51*(1-T51),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V51" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W51" s="11">
         <f>IFERROR(VLOOKUP(V51,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X51" s="12">
-        <f>ROUND(U51*W51,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y51" s="26">
-        <f>Q51</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z51" s="12">
-        <f>ROUND(Y51*R51,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA51" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB51" s="11">
         <f>IFERROR(VLOOKUP(AA51,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC51" s="12">
-        <f>ROUND(Y51*AB51*R51,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD51" s="12">
-        <f>ROUND(AC51-X51,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE51" s="13">
-        <f>IFERROR(AD51/AC51,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:31" x14ac:dyDescent="0.25">
@@ -3563,43 +4013,53 @@
         <v>0</v>
       </c>
       <c r="S52" s="12">
-        <f>ROUND(Q52*R52,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T52" s="5">
         <v>0</v>
       </c>
       <c r="U52" s="12">
-        <f>ROUND(S52*(1-T52),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V52" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W52" s="11">
         <f>IFERROR(VLOOKUP(V52,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X52" s="12">
-        <f>ROUND(U52*W52,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y52" s="26">
-        <f>Q52</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z52" s="12">
-        <f>ROUND(Y52*R52,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB52" s="11">
         <f>IFERROR(VLOOKUP(AA52,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC52" s="12">
-        <f>ROUND(Y52*AB52*R52,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD52" s="12">
-        <f>ROUND(AC52-X52,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE52" s="13">
-        <f>IFERROR(AD52/AC52,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:31" x14ac:dyDescent="0.25">
@@ -3621,43 +4081,53 @@
         <v>0</v>
       </c>
       <c r="S53" s="12">
-        <f>ROUND(Q53*R53,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T53" s="5">
         <v>0</v>
       </c>
       <c r="U53" s="12">
-        <f>ROUND(S53*(1-T53),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V53" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W53" s="11">
         <f>IFERROR(VLOOKUP(V53,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X53" s="12">
-        <f>ROUND(U53*W53,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y53" s="26">
-        <f>Q53</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z53" s="12">
-        <f>ROUND(Y53*R53,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA53" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB53" s="11">
         <f>IFERROR(VLOOKUP(AA53,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC53" s="12">
-        <f>ROUND(Y53*AB53*R53,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD53" s="12">
-        <f>ROUND(AC53-X53,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE53" s="13">
-        <f>IFERROR(AD53/AC53,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:31" x14ac:dyDescent="0.25">
@@ -3679,43 +4149,53 @@
         <v>0</v>
       </c>
       <c r="S54" s="12">
-        <f>ROUND(Q54*R54,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T54" s="5">
         <v>0</v>
       </c>
       <c r="U54" s="12">
-        <f>ROUND(S54*(1-T54),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V54" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W54" s="11">
         <f>IFERROR(VLOOKUP(V54,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X54" s="12">
-        <f>ROUND(U54*W54,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y54" s="26">
-        <f>Q54</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z54" s="12">
-        <f>ROUND(Y54*R54,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA54" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB54" s="11">
         <f>IFERROR(VLOOKUP(AA54,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC54" s="12">
-        <f>ROUND(Y54*AB54*R54,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD54" s="12">
-        <f>ROUND(AC54-X54,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE54" s="13">
-        <f>IFERROR(AD54/AC54,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:31" x14ac:dyDescent="0.25">
@@ -3737,43 +4217,53 @@
         <v>0</v>
       </c>
       <c r="S55" s="12">
-        <f>ROUND(Q55*R55,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T55" s="5">
         <v>0</v>
       </c>
       <c r="U55" s="12">
-        <f>ROUND(S55*(1-T55),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V55" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W55" s="11">
         <f>IFERROR(VLOOKUP(V55,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X55" s="12">
-        <f>ROUND(U55*W55,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y55" s="26">
-        <f>Q55</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z55" s="12">
-        <f>ROUND(Y55*R55,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB55" s="11">
         <f>IFERROR(VLOOKUP(AA55,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC55" s="12">
-        <f>ROUND(Y55*AB55*R55,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD55" s="12">
-        <f>ROUND(AC55-X55,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE55" s="13">
-        <f>IFERROR(AD55/AC55,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:31" x14ac:dyDescent="0.25">
@@ -3795,43 +4285,53 @@
         <v>0</v>
       </c>
       <c r="S56" s="12">
-        <f>ROUND(Q56*R56,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T56" s="5">
         <v>0</v>
       </c>
       <c r="U56" s="12">
-        <f>ROUND(S56*(1-T56),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V56" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W56" s="11">
         <f>IFERROR(VLOOKUP(V56,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X56" s="12">
-        <f>ROUND(U56*W56,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y56" s="26">
-        <f>Q56</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z56" s="12">
-        <f>ROUND(Y56*R56,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB56" s="11">
         <f>IFERROR(VLOOKUP(AA56,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC56" s="12">
-        <f>ROUND(Y56*AB56*R56,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD56" s="12">
-        <f>ROUND(AC56-X56,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE56" s="13">
-        <f>IFERROR(AD56/AC56,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:31" x14ac:dyDescent="0.25">
@@ -3853,43 +4353,53 @@
         <v>0</v>
       </c>
       <c r="S57" s="12">
-        <f>ROUND(Q57*R57,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T57" s="5">
         <v>0</v>
       </c>
       <c r="U57" s="12">
-        <f>ROUND(S57*(1-T57),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V57" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W57" s="11">
         <f>IFERROR(VLOOKUP(V57,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X57" s="12">
-        <f>ROUND(U57*W57,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y57" s="26">
-        <f>Q57</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z57" s="12">
-        <f>ROUND(Y57*R57,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA57" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB57" s="11">
         <f>IFERROR(VLOOKUP(AA57,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC57" s="12">
-        <f>ROUND(Y57*AB57*R57,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD57" s="12">
-        <f>ROUND(AC57-X57,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE57" s="13">
-        <f>IFERROR(AD57/AC57,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:31" x14ac:dyDescent="0.25">
@@ -3911,43 +4421,53 @@
         <v>0</v>
       </c>
       <c r="S58" s="12">
-        <f>ROUND(Q58*R58,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T58" s="5">
         <v>0</v>
       </c>
       <c r="U58" s="12">
-        <f>ROUND(S58*(1-T58),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V58" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W58" s="11">
         <f>IFERROR(VLOOKUP(V58,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X58" s="12">
-        <f>ROUND(U58*W58,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y58" s="26">
-        <f>Q58</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z58" s="12">
-        <f>ROUND(Y58*R58,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB58" s="11">
         <f>IFERROR(VLOOKUP(AA58,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC58" s="12">
-        <f>ROUND(Y58*AB58*R58,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD58" s="12">
-        <f>ROUND(AC58-X58,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE58" s="13">
-        <f>IFERROR(AD58/AC58,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:31" x14ac:dyDescent="0.25">
@@ -3969,43 +4489,53 @@
         <v>0</v>
       </c>
       <c r="S59" s="12">
-        <f>ROUND(Q59*R59,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T59" s="5">
         <v>0</v>
       </c>
       <c r="U59" s="12">
-        <f>ROUND(S59*(1-T59),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V59" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W59" s="11">
         <f>IFERROR(VLOOKUP(V59,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X59" s="12">
-        <f>ROUND(U59*W59,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y59" s="26">
-        <f>Q59</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z59" s="12">
-        <f>ROUND(Y59*R59,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA59" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB59" s="11">
         <f>IFERROR(VLOOKUP(AA59,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC59" s="12">
-        <f>ROUND(Y59*AB59*R59,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD59" s="12">
-        <f>ROUND(AC59-X59,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE59" s="13">
-        <f>IFERROR(AD59/AC59,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:31" x14ac:dyDescent="0.25">
@@ -4027,43 +4557,53 @@
         <v>0</v>
       </c>
       <c r="S60" s="12">
-        <f>ROUND(Q60*R60,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T60" s="5">
         <v>0</v>
       </c>
       <c r="U60" s="12">
-        <f>ROUND(S60*(1-T60),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V60" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W60" s="11">
         <f>IFERROR(VLOOKUP(V60,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X60" s="12">
-        <f>ROUND(U60*W60,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y60" s="26">
-        <f>Q60</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z60" s="12">
-        <f>ROUND(Y60*R60,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB60" s="11">
         <f>IFERROR(VLOOKUP(AA60,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC60" s="12">
-        <f>ROUND(Y60*AB60*R60,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD60" s="12">
-        <f>ROUND(AC60-X60,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE60" s="13">
-        <f>IFERROR(AD60/AC60,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:31" x14ac:dyDescent="0.25">
@@ -4085,43 +4625,53 @@
         <v>0</v>
       </c>
       <c r="S61" s="12">
-        <f>ROUND(Q61*R61,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T61" s="5">
         <v>0</v>
       </c>
       <c r="U61" s="12">
-        <f>ROUND(S61*(1-T61),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V61" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W61" s="11">
         <f>IFERROR(VLOOKUP(V61,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X61" s="12">
-        <f>ROUND(U61*W61,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y61" s="26">
-        <f>Q61</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z61" s="12">
-        <f>ROUND(Y61*R61,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA61" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB61" s="11">
         <f>IFERROR(VLOOKUP(AA61,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC61" s="12">
-        <f>ROUND(Y61*AB61*R61,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD61" s="12">
-        <f>ROUND(AC61-X61,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE61" s="13">
-        <f>IFERROR(AD61/AC61,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:31" x14ac:dyDescent="0.25">
@@ -4143,43 +4693,53 @@
         <v>0</v>
       </c>
       <c r="S62" s="12">
-        <f>ROUND(Q62*R62,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T62" s="5">
         <v>0</v>
       </c>
       <c r="U62" s="12">
-        <f>ROUND(S62*(1-T62),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V62" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W62" s="11">
         <f>IFERROR(VLOOKUP(V62,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X62" s="12">
-        <f>ROUND(U62*W62,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y62" s="26">
-        <f>Q62</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z62" s="12">
-        <f>ROUND(Y62*R62,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA62" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB62" s="11">
         <f>IFERROR(VLOOKUP(AA62,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC62" s="12">
-        <f>ROUND(Y62*AB62*R62,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD62" s="12">
-        <f>ROUND(AC62-X62,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE62" s="13">
-        <f>IFERROR(AD62/AC62,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:31" x14ac:dyDescent="0.25">
@@ -4201,43 +4761,53 @@
         <v>0</v>
       </c>
       <c r="S63" s="12">
-        <f>ROUND(Q63*R63,2)</f>
+        <f t="shared" ref="S63:S98" si="22">+Q63*R63</f>
+        <v>0</v>
       </c>
       <c r="T63" s="5">
         <v>0</v>
       </c>
       <c r="U63" s="12">
-        <f>ROUND(S63*(1-T63),2)</f>
+        <f t="shared" ref="U63:U98" si="23">S63*(1-T63)</f>
+        <v>0</v>
       </c>
       <c r="V63" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W63" s="11">
         <f>IFERROR(VLOOKUP(V63,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X63" s="12">
-        <f>ROUND(U63*W63,2)</f>
+        <f t="shared" ref="X63:X98" si="24">U63*W63</f>
+        <v>0</v>
       </c>
       <c r="Y63" s="26">
-        <f>Q63</f>
+        <f t="shared" ref="Y63:Y98" si="25">Q63</f>
+        <v>0</v>
       </c>
       <c r="Z63" s="12">
-        <f>ROUND(Y63*R63,2)</f>
+        <f t="shared" ref="Z63:Z98" si="26">+Y63*R63</f>
+        <v>0</v>
       </c>
       <c r="AA63" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB63" s="11">
         <f>IFERROR(VLOOKUP(AA63,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC63" s="12">
-        <f>ROUND(Y63*AB63*R63,2)</f>
+        <f t="shared" ref="AC63:AC98" si="27">+Y63*AB63*R63</f>
+        <v>0</v>
       </c>
       <c r="AD63" s="12">
-        <f>ROUND(AC63-X63,2)</f>
+        <f t="shared" ref="AD63:AD98" si="28">+AC63-X63</f>
+        <v>0</v>
       </c>
       <c r="AE63" s="13">
-        <f>IFERROR(AD63/AC63,0)</f>
+        <f t="shared" ref="AE63:AE98" si="29">IFERROR(AD63/AC63,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:31" x14ac:dyDescent="0.25">
@@ -4259,43 +4829,53 @@
         <v>0</v>
       </c>
       <c r="S64" s="12">
-        <f>ROUND(Q64*R64,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T64" s="5">
         <v>0</v>
       </c>
       <c r="U64" s="12">
-        <f>ROUND(S64*(1-T64),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V64" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W64" s="11">
         <f>IFERROR(VLOOKUP(V64,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X64" s="12">
-        <f>ROUND(U64*W64,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y64" s="26">
-        <f>Q64</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z64" s="12">
-        <f>ROUND(Y64*R64,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA64" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB64" s="11">
         <f>IFERROR(VLOOKUP(AA64,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC64" s="12">
-        <f>ROUND(Y64*AB64*R64,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD64" s="12">
-        <f>ROUND(AC64-X64,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE64" s="13">
-        <f>IFERROR(AD64/AC64,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:31" x14ac:dyDescent="0.25">
@@ -4317,43 +4897,53 @@
         <v>0</v>
       </c>
       <c r="S65" s="12">
-        <f>ROUND(Q65*R65,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T65" s="5">
         <v>0</v>
       </c>
       <c r="U65" s="12">
-        <f>ROUND(S65*(1-T65),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V65" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W65" s="11">
         <f>IFERROR(VLOOKUP(V65,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X65" s="12">
-        <f>ROUND(U65*W65,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y65" s="26">
-        <f>Q65</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z65" s="12">
-        <f>ROUND(Y65*R65,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA65" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB65" s="11">
         <f>IFERROR(VLOOKUP(AA65,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC65" s="12">
-        <f>ROUND(Y65*AB65*R65,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD65" s="12">
-        <f>ROUND(AC65-X65,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE65" s="13">
-        <f>IFERROR(AD65/AC65,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:31" x14ac:dyDescent="0.25">
@@ -4375,43 +4965,53 @@
         <v>0</v>
       </c>
       <c r="S66" s="12">
-        <f>ROUND(Q66*R66,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T66" s="5">
         <v>0</v>
       </c>
       <c r="U66" s="12">
-        <f>ROUND(S66*(1-T66),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V66" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W66" s="11">
         <f>IFERROR(VLOOKUP(V66,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X66" s="12">
-        <f>ROUND(U66*W66,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y66" s="26">
-        <f>Q66</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z66" s="12">
-        <f>ROUND(Y66*R66,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA66" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB66" s="11">
         <f>IFERROR(VLOOKUP(AA66,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC66" s="12">
-        <f>ROUND(Y66*AB66*R66,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD66" s="12">
-        <f>ROUND(AC66-X66,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE66" s="13">
-        <f>IFERROR(AD66/AC66,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:31" x14ac:dyDescent="0.25">
@@ -4433,43 +5033,53 @@
         <v>0</v>
       </c>
       <c r="S67" s="12">
-        <f>ROUND(Q67*R67,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T67" s="5">
         <v>0</v>
       </c>
       <c r="U67" s="12">
-        <f>ROUND(S67*(1-T67),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V67" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W67" s="11">
         <f>IFERROR(VLOOKUP(V67,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X67" s="12">
-        <f>ROUND(U67*W67,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y67" s="26">
-        <f>Q67</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z67" s="12">
-        <f>ROUND(Y67*R67,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA67" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB67" s="11">
         <f>IFERROR(VLOOKUP(AA67,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC67" s="12">
-        <f>ROUND(Y67*AB67*R67,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD67" s="12">
-        <f>ROUND(AC67-X67,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE67" s="13">
-        <f>IFERROR(AD67/AC67,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:31" x14ac:dyDescent="0.25">
@@ -4491,43 +5101,53 @@
         <v>0</v>
       </c>
       <c r="S68" s="12">
-        <f>ROUND(Q68*R68,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T68" s="5">
         <v>0</v>
       </c>
       <c r="U68" s="12">
-        <f>ROUND(S68*(1-T68),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V68" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W68" s="11">
         <f>IFERROR(VLOOKUP(V68,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X68" s="12">
-        <f>ROUND(U68*W68,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y68" s="26">
-        <f>Q68</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z68" s="12">
-        <f>ROUND(Y68*R68,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA68" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB68" s="11">
         <f>IFERROR(VLOOKUP(AA68,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC68" s="12">
-        <f>ROUND(Y68*AB68*R68,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD68" s="12">
-        <f>ROUND(AC68-X68,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE68" s="13">
-        <f>IFERROR(AD68/AC68,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:31" x14ac:dyDescent="0.25">
@@ -4549,43 +5169,53 @@
         <v>0</v>
       </c>
       <c r="S69" s="12">
-        <f>ROUND(Q69*R69,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T69" s="5">
         <v>0</v>
       </c>
       <c r="U69" s="12">
-        <f>ROUND(S69*(1-T69),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V69" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W69" s="11">
         <f>IFERROR(VLOOKUP(V69,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X69" s="12">
-        <f>ROUND(U69*W69,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y69" s="26">
-        <f>Q69</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z69" s="12">
-        <f>ROUND(Y69*R69,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA69" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB69" s="11">
         <f>IFERROR(VLOOKUP(AA69,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC69" s="12">
-        <f>ROUND(Y69*AB69*R69,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD69" s="12">
-        <f>ROUND(AC69-X69,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE69" s="13">
-        <f>IFERROR(AD69/AC69,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:31" x14ac:dyDescent="0.25">
@@ -4607,43 +5237,53 @@
         <v>0</v>
       </c>
       <c r="S70" s="12">
-        <f>ROUND(Q70*R70,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T70" s="5">
         <v>0</v>
       </c>
       <c r="U70" s="12">
-        <f>ROUND(S70*(1-T70),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V70" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W70" s="11">
         <f>IFERROR(VLOOKUP(V70,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X70" s="12">
-        <f>ROUND(U70*W70,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y70" s="26">
-        <f>Q70</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z70" s="12">
-        <f>ROUND(Y70*R70,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA70" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB70" s="11">
         <f>IFERROR(VLOOKUP(AA70,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC70" s="12">
-        <f>ROUND(Y70*AB70*R70,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD70" s="12">
-        <f>ROUND(AC70-X70,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE70" s="13">
-        <f>IFERROR(AD70/AC70,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:31" x14ac:dyDescent="0.25">
@@ -4665,43 +5305,53 @@
         <v>0</v>
       </c>
       <c r="S71" s="12">
-        <f>ROUND(Q71*R71,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T71" s="5">
         <v>0</v>
       </c>
       <c r="U71" s="12">
-        <f>ROUND(S71*(1-T71),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V71" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W71" s="11">
         <f>IFERROR(VLOOKUP(V71,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X71" s="12">
-        <f>ROUND(U71*W71,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y71" s="26">
-        <f>Q71</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z71" s="12">
-        <f>ROUND(Y71*R71,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB71" s="11">
         <f>IFERROR(VLOOKUP(AA71,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC71" s="12">
-        <f>ROUND(Y71*AB71*R71,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD71" s="12">
-        <f>ROUND(AC71-X71,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE71" s="13">
-        <f>IFERROR(AD71/AC71,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:31" x14ac:dyDescent="0.25">
@@ -4723,43 +5373,53 @@
         <v>0</v>
       </c>
       <c r="S72" s="12">
-        <f>ROUND(Q72*R72,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T72" s="5">
         <v>0</v>
       </c>
       <c r="U72" s="12">
-        <f>ROUND(S72*(1-T72),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V72" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W72" s="11">
         <f>IFERROR(VLOOKUP(V72,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X72" s="12">
-        <f>ROUND(U72*W72,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y72" s="26">
-        <f>Q72</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z72" s="12">
-        <f>ROUND(Y72*R72,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA72" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB72" s="11">
         <f>IFERROR(VLOOKUP(AA72,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC72" s="12">
-        <f>ROUND(Y72*AB72*R72,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD72" s="12">
-        <f>ROUND(AC72-X72,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE72" s="13">
-        <f>IFERROR(AD72/AC72,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:31" x14ac:dyDescent="0.25">
@@ -4781,43 +5441,53 @@
         <v>0</v>
       </c>
       <c r="S73" s="12">
-        <f>ROUND(Q73*R73,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T73" s="5">
         <v>0</v>
       </c>
       <c r="U73" s="12">
-        <f>ROUND(S73*(1-T73),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V73" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W73" s="11">
         <f>IFERROR(VLOOKUP(V73,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X73" s="12">
-        <f>ROUND(U73*W73,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y73" s="26">
-        <f>Q73</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z73" s="12">
-        <f>ROUND(Y73*R73,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA73" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB73" s="11">
         <f>IFERROR(VLOOKUP(AA73,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC73" s="12">
-        <f>ROUND(Y73*AB73*R73,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD73" s="12">
-        <f>ROUND(AC73-X73,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE73" s="13">
-        <f>IFERROR(AD73/AC73,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="2:31" x14ac:dyDescent="0.25">
@@ -4839,43 +5509,53 @@
         <v>0</v>
       </c>
       <c r="S74" s="12">
-        <f>ROUND(Q74*R74,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T74" s="5">
         <v>0</v>
       </c>
       <c r="U74" s="12">
-        <f>ROUND(S74*(1-T74),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V74" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W74" s="11">
         <f>IFERROR(VLOOKUP(V74,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X74" s="12">
-        <f>ROUND(U74*W74,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y74" s="26">
-        <f>Q74</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z74" s="12">
-        <f>ROUND(Y74*R74,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB74" s="11">
         <f>IFERROR(VLOOKUP(AA74,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC74" s="12">
-        <f>ROUND(Y74*AB74*R74,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD74" s="12">
-        <f>ROUND(AC74-X74,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE74" s="13">
-        <f>IFERROR(AD74/AC74,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:31" x14ac:dyDescent="0.25">
@@ -4897,43 +5577,53 @@
         <v>0</v>
       </c>
       <c r="S75" s="12">
-        <f>ROUND(Q75*R75,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T75" s="5">
         <v>0</v>
       </c>
       <c r="U75" s="12">
-        <f>ROUND(S75*(1-T75),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V75" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W75" s="11">
         <f>IFERROR(VLOOKUP(V75,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X75" s="12">
-        <f>ROUND(U75*W75,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y75" s="26">
-        <f>Q75</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z75" s="12">
-        <f>ROUND(Y75*R75,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB75" s="11">
         <f>IFERROR(VLOOKUP(AA75,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC75" s="12">
-        <f>ROUND(Y75*AB75*R75,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD75" s="12">
-        <f>ROUND(AC75-X75,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE75" s="13">
-        <f>IFERROR(AD75/AC75,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="2:31" x14ac:dyDescent="0.25">
@@ -4955,43 +5645,53 @@
         <v>0</v>
       </c>
       <c r="S76" s="12">
-        <f>ROUND(Q76*R76,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T76" s="5">
         <v>0</v>
       </c>
       <c r="U76" s="12">
-        <f>ROUND(S76*(1-T76),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V76" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W76" s="11">
         <f>IFERROR(VLOOKUP(V76,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X76" s="12">
-        <f>ROUND(U76*W76,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y76" s="26">
-        <f>Q76</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z76" s="12">
-        <f>ROUND(Y76*R76,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB76" s="11">
         <f>IFERROR(VLOOKUP(AA76,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC76" s="12">
-        <f>ROUND(Y76*AB76*R76,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD76" s="12">
-        <f>ROUND(AC76-X76,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE76" s="13">
-        <f>IFERROR(AD76/AC76,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="2:31" x14ac:dyDescent="0.25">
@@ -5013,43 +5713,53 @@
         <v>0</v>
       </c>
       <c r="S77" s="12">
-        <f>ROUND(Q77*R77,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T77" s="5">
         <v>0</v>
       </c>
       <c r="U77" s="12">
-        <f>ROUND(S77*(1-T77),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V77" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W77" s="11">
         <f>IFERROR(VLOOKUP(V77,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X77" s="12">
-        <f>ROUND(U77*W77,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y77" s="26">
-        <f>Q77</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z77" s="12">
-        <f>ROUND(Y77*R77,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB77" s="11">
         <f>IFERROR(VLOOKUP(AA77,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC77" s="12">
-        <f>ROUND(Y77*AB77*R77,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD77" s="12">
-        <f>ROUND(AC77-X77,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE77" s="13">
-        <f>IFERROR(AD77/AC77,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="2:31" x14ac:dyDescent="0.25">
@@ -5071,43 +5781,53 @@
         <v>0</v>
       </c>
       <c r="S78" s="12">
-        <f>ROUND(Q78*R78,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T78" s="5">
         <v>0</v>
       </c>
       <c r="U78" s="12">
-        <f>ROUND(S78*(1-T78),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V78" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W78" s="11">
         <f>IFERROR(VLOOKUP(V78,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X78" s="12">
-        <f>ROUND(U78*W78,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y78" s="26">
-        <f>Q78</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z78" s="12">
-        <f>ROUND(Y78*R78,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA78" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB78" s="11">
         <f>IFERROR(VLOOKUP(AA78,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC78" s="12">
-        <f>ROUND(Y78*AB78*R78,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD78" s="12">
-        <f>ROUND(AC78-X78,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE78" s="13">
-        <f>IFERROR(AD78/AC78,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="2:31" x14ac:dyDescent="0.25">
@@ -5129,43 +5849,53 @@
         <v>0</v>
       </c>
       <c r="S79" s="12">
-        <f>ROUND(Q79*R79,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T79" s="5">
         <v>0</v>
       </c>
       <c r="U79" s="12">
-        <f>ROUND(S79*(1-T79),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V79" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W79" s="11">
         <f>IFERROR(VLOOKUP(V79,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X79" s="12">
-        <f>ROUND(U79*W79,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y79" s="26">
-        <f>Q79</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z79" s="12">
-        <f>ROUND(Y79*R79,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA79" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB79" s="11">
         <f>IFERROR(VLOOKUP(AA79,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC79" s="12">
-        <f>ROUND(Y79*AB79*R79,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD79" s="12">
-        <f>ROUND(AC79-X79,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE79" s="13">
-        <f>IFERROR(AD79/AC79,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:31" x14ac:dyDescent="0.25">
@@ -5187,43 +5917,53 @@
         <v>0</v>
       </c>
       <c r="S80" s="12">
-        <f>ROUND(Q80*R80,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T80" s="5">
         <v>0</v>
       </c>
       <c r="U80" s="12">
-        <f>ROUND(S80*(1-T80),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V80" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W80" s="11">
         <f>IFERROR(VLOOKUP(V80,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X80" s="12">
-        <f>ROUND(U80*W80,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y80" s="26">
-        <f>Q80</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z80" s="12">
-        <f>ROUND(Y80*R80,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB80" s="11">
         <f>IFERROR(VLOOKUP(AA80,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC80" s="12">
-        <f>ROUND(Y80*AB80*R80,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD80" s="12">
-        <f>ROUND(AC80-X80,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE80" s="13">
-        <f>IFERROR(AD80/AC80,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:31" x14ac:dyDescent="0.25">
@@ -5245,43 +5985,53 @@
         <v>0</v>
       </c>
       <c r="S81" s="12">
-        <f>ROUND(Q81*R81,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T81" s="5">
         <v>0</v>
       </c>
       <c r="U81" s="12">
-        <f>ROUND(S81*(1-T81),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V81" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W81" s="11">
         <f>IFERROR(VLOOKUP(V81,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X81" s="12">
-        <f>ROUND(U81*W81,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y81" s="26">
-        <f>Q81</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z81" s="12">
-        <f>ROUND(Y81*R81,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA81" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB81" s="11">
         <f>IFERROR(VLOOKUP(AA81,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC81" s="12">
-        <f>ROUND(Y81*AB81*R81,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD81" s="12">
-        <f>ROUND(AC81-X81,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE81" s="13">
-        <f>IFERROR(AD81/AC81,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="2:31" x14ac:dyDescent="0.25">
@@ -5303,43 +6053,53 @@
         <v>0</v>
       </c>
       <c r="S82" s="12">
-        <f>ROUND(Q82*R82,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T82" s="5">
         <v>0</v>
       </c>
       <c r="U82" s="12">
-        <f>ROUND(S82*(1-T82),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V82" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W82" s="11">
         <f>IFERROR(VLOOKUP(V82,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X82" s="12">
-        <f>ROUND(U82*W82,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y82" s="26">
-        <f>Q82</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z82" s="12">
-        <f>ROUND(Y82*R82,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB82" s="11">
         <f>IFERROR(VLOOKUP(AA82,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC82" s="12">
-        <f>ROUND(Y82*AB82*R82,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD82" s="12">
-        <f>ROUND(AC82-X82,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE82" s="13">
-        <f>IFERROR(AD82/AC82,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:31" x14ac:dyDescent="0.25">
@@ -5361,43 +6121,53 @@
         <v>0</v>
       </c>
       <c r="S83" s="12">
-        <f>ROUND(Q83*R83,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T83" s="5">
         <v>0</v>
       </c>
       <c r="U83" s="12">
-        <f>ROUND(S83*(1-T83),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V83" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W83" s="11">
         <f>IFERROR(VLOOKUP(V83,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X83" s="12">
-        <f>ROUND(U83*W83,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y83" s="26">
-        <f>Q83</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z83" s="12">
-        <f>ROUND(Y83*R83,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB83" s="11">
         <f>IFERROR(VLOOKUP(AA83,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC83" s="12">
-        <f>ROUND(Y83*AB83*R83,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD83" s="12">
-        <f>ROUND(AC83-X83,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE83" s="13">
-        <f>IFERROR(AD83/AC83,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="2:31" x14ac:dyDescent="0.25">
@@ -5419,43 +6189,53 @@
         <v>0</v>
       </c>
       <c r="S84" s="12">
-        <f>ROUND(Q84*R84,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T84" s="5">
         <v>0</v>
       </c>
       <c r="U84" s="12">
-        <f>ROUND(S84*(1-T84),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V84" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W84" s="11">
         <f>IFERROR(VLOOKUP(V84,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X84" s="12">
-        <f>ROUND(U84*W84,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y84" s="26">
-        <f>Q84</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z84" s="12">
-        <f>ROUND(Y84*R84,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA84" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB84" s="11">
         <f>IFERROR(VLOOKUP(AA84,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC84" s="12">
-        <f>ROUND(Y84*AB84*R84,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD84" s="12">
-        <f>ROUND(AC84-X84,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE84" s="13">
-        <f>IFERROR(AD84/AC84,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="2:31" x14ac:dyDescent="0.25">
@@ -5477,43 +6257,53 @@
         <v>0</v>
       </c>
       <c r="S85" s="12">
-        <f>ROUND(Q85*R85,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T85" s="5">
         <v>0</v>
       </c>
       <c r="U85" s="12">
-        <f>ROUND(S85*(1-T85),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V85" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W85" s="11">
         <f>IFERROR(VLOOKUP(V85,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X85" s="12">
-        <f>ROUND(U85*W85,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y85" s="26">
-        <f>Q85</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z85" s="12">
-        <f>ROUND(Y85*R85,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB85" s="11">
         <f>IFERROR(VLOOKUP(AA85,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC85" s="12">
-        <f>ROUND(Y85*AB85*R85,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD85" s="12">
-        <f>ROUND(AC85-X85,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE85" s="13">
-        <f>IFERROR(AD85/AC85,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="2:31" x14ac:dyDescent="0.25">
@@ -5535,43 +6325,53 @@
         <v>0</v>
       </c>
       <c r="S86" s="12">
-        <f>ROUND(Q86*R86,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T86" s="5">
         <v>0</v>
       </c>
       <c r="U86" s="12">
-        <f>ROUND(S86*(1-T86),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V86" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W86" s="11">
         <f>IFERROR(VLOOKUP(V86,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X86" s="12">
-        <f>ROUND(U86*W86,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y86" s="26">
-        <f>Q86</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z86" s="12">
-        <f>ROUND(Y86*R86,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB86" s="11">
         <f>IFERROR(VLOOKUP(AA86,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC86" s="12">
-        <f>ROUND(Y86*AB86*R86,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD86" s="12">
-        <f>ROUND(AC86-X86,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE86" s="13">
-        <f>IFERROR(AD86/AC86,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="2:31" x14ac:dyDescent="0.25">
@@ -5593,43 +6393,53 @@
         <v>0</v>
       </c>
       <c r="S87" s="12">
-        <f>ROUND(Q87*R87,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T87" s="5">
         <v>0</v>
       </c>
       <c r="U87" s="12">
-        <f>ROUND(S87*(1-T87),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V87" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W87" s="11">
         <f>IFERROR(VLOOKUP(V87,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X87" s="12">
-        <f>ROUND(U87*W87,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y87" s="26">
-        <f>Q87</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z87" s="12">
-        <f>ROUND(Y87*R87,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB87" s="11">
         <f>IFERROR(VLOOKUP(AA87,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC87" s="12">
-        <f>ROUND(Y87*AB87*R87,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD87" s="12">
-        <f>ROUND(AC87-X87,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE87" s="13">
-        <f>IFERROR(AD87/AC87,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="2:31" x14ac:dyDescent="0.25">
@@ -5651,43 +6461,53 @@
         <v>0</v>
       </c>
       <c r="S88" s="12">
-        <f>ROUND(Q88*R88,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T88" s="5">
         <v>0</v>
       </c>
       <c r="U88" s="12">
-        <f>ROUND(S88*(1-T88),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V88" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W88" s="11">
         <f>IFERROR(VLOOKUP(V88,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X88" s="12">
-        <f>ROUND(U88*W88,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y88" s="26">
-        <f>Q88</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z88" s="12">
-        <f>ROUND(Y88*R88,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB88" s="11">
         <f>IFERROR(VLOOKUP(AA88,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC88" s="12">
-        <f>ROUND(Y88*AB88*R88,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD88" s="12">
-        <f>ROUND(AC88-X88,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE88" s="13">
-        <f>IFERROR(AD88/AC88,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="2:31" x14ac:dyDescent="0.25">
@@ -5709,43 +6529,53 @@
         <v>0</v>
       </c>
       <c r="S89" s="12">
-        <f>ROUND(Q89*R89,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T89" s="5">
         <v>0</v>
       </c>
       <c r="U89" s="12">
-        <f>ROUND(S89*(1-T89),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V89" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W89" s="11">
         <f>IFERROR(VLOOKUP(V89,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X89" s="12">
-        <f>ROUND(U89*W89,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y89" s="26">
-        <f>Q89</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z89" s="12">
-        <f>ROUND(Y89*R89,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB89" s="11">
         <f>IFERROR(VLOOKUP(AA89,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC89" s="12">
-        <f>ROUND(Y89*AB89*R89,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD89" s="12">
-        <f>ROUND(AC89-X89,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE89" s="13">
-        <f>IFERROR(AD89/AC89,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="2:31" x14ac:dyDescent="0.25">
@@ -5767,43 +6597,53 @@
         <v>0</v>
       </c>
       <c r="S90" s="12">
-        <f>ROUND(Q90*R90,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T90" s="5">
         <v>0</v>
       </c>
       <c r="U90" s="12">
-        <f>ROUND(S90*(1-T90),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V90" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W90" s="11">
         <f>IFERROR(VLOOKUP(V90,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X90" s="12">
-        <f>ROUND(U90*W90,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y90" s="26">
-        <f>Q90</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z90" s="12">
-        <f>ROUND(Y90*R90,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB90" s="11">
         <f>IFERROR(VLOOKUP(AA90,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC90" s="12">
-        <f>ROUND(Y90*AB90*R90,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD90" s="12">
-        <f>ROUND(AC90-X90,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE90" s="13">
-        <f>IFERROR(AD90/AC90,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="2:31" x14ac:dyDescent="0.25">
@@ -5825,43 +6665,53 @@
         <v>0</v>
       </c>
       <c r="S91" s="12">
-        <f>ROUND(Q91*R91,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T91" s="5">
         <v>0</v>
       </c>
       <c r="U91" s="12">
-        <f>ROUND(S91*(1-T91),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V91" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W91" s="11">
         <f>IFERROR(VLOOKUP(V91,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X91" s="12">
-        <f>ROUND(U91*W91,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y91" s="26">
-        <f>Q91</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z91" s="12">
-        <f>ROUND(Y91*R91,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA91" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB91" s="11">
         <f>IFERROR(VLOOKUP(AA91,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC91" s="12">
-        <f>ROUND(Y91*AB91*R91,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD91" s="12">
-        <f>ROUND(AC91-X91,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE91" s="13">
-        <f>IFERROR(AD91/AC91,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="2:31" x14ac:dyDescent="0.25">
@@ -5883,43 +6733,53 @@
         <v>0</v>
       </c>
       <c r="S92" s="12">
-        <f>ROUND(Q92*R92,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T92" s="5">
         <v>0</v>
       </c>
       <c r="U92" s="12">
-        <f>ROUND(S92*(1-T92),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V92" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W92" s="11">
         <f>IFERROR(VLOOKUP(V92,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X92" s="12">
-        <f>ROUND(U92*W92,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y92" s="26">
-        <f>Q92</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z92" s="12">
-        <f>ROUND(Y92*R92,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA92" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB92" s="11">
         <f>IFERROR(VLOOKUP(AA92,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC92" s="12">
-        <f>ROUND(Y92*AB92*R92,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD92" s="12">
-        <f>ROUND(AC92-X92,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE92" s="13">
-        <f>IFERROR(AD92/AC92,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="2:31" x14ac:dyDescent="0.25">
@@ -5941,43 +6801,53 @@
         <v>0</v>
       </c>
       <c r="S93" s="12">
-        <f>ROUND(Q93*R93,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T93" s="5">
         <v>0</v>
       </c>
       <c r="U93" s="12">
-        <f>ROUND(S93*(1-T93),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V93" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W93" s="11">
         <f>IFERROR(VLOOKUP(V93,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X93" s="12">
-        <f>ROUND(U93*W93,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y93" s="26">
-        <f>Q93</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z93" s="12">
-        <f>ROUND(Y93*R93,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB93" s="11">
         <f>IFERROR(VLOOKUP(AA93,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC93" s="12">
-        <f>ROUND(Y93*AB93*R93,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD93" s="12">
-        <f>ROUND(AC93-X93,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE93" s="13">
-        <f>IFERROR(AD93/AC93,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="2:31" x14ac:dyDescent="0.25">
@@ -5999,43 +6869,53 @@
         <v>0</v>
       </c>
       <c r="S94" s="12">
-        <f>ROUND(Q94*R94,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T94" s="5">
         <v>0</v>
       </c>
       <c r="U94" s="12">
-        <f>ROUND(S94*(1-T94),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V94" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W94" s="11">
         <f>IFERROR(VLOOKUP(V94,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X94" s="12">
-        <f>ROUND(U94*W94,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y94" s="26">
-        <f>Q94</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z94" s="12">
-        <f>ROUND(Y94*R94,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA94" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB94" s="11">
         <f>IFERROR(VLOOKUP(AA94,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC94" s="12">
-        <f>ROUND(Y94*AB94*R94,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD94" s="12">
-        <f>ROUND(AC94-X94,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE94" s="13">
-        <f>IFERROR(AD94/AC94,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="2:31" x14ac:dyDescent="0.25">
@@ -6057,43 +6937,53 @@
         <v>0</v>
       </c>
       <c r="S95" s="12">
-        <f>ROUND(Q95*R95,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T95" s="5">
         <v>0</v>
       </c>
       <c r="U95" s="12">
-        <f>ROUND(S95*(1-T95),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V95" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W95" s="11">
         <f>IFERROR(VLOOKUP(V95,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X95" s="12">
-        <f>ROUND(U95*W95,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y95" s="26">
-        <f>Q95</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z95" s="12">
-        <f>ROUND(Y95*R95,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA95" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB95" s="11">
         <f>IFERROR(VLOOKUP(AA95,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC95" s="12">
-        <f>ROUND(Y95*AB95*R95,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD95" s="12">
-        <f>ROUND(AC95-X95,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE95" s="13">
-        <f>IFERROR(AD95/AC95,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="2:31" x14ac:dyDescent="0.25">
@@ -6115,43 +7005,53 @@
         <v>0</v>
       </c>
       <c r="S96" s="12">
-        <f>ROUND(Q96*R96,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T96" s="5">
         <v>0</v>
       </c>
       <c r="U96" s="12">
-        <f>ROUND(S96*(1-T96),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V96" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W96" s="11">
         <f>IFERROR(VLOOKUP(V96,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X96" s="12">
-        <f>ROUND(U96*W96,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y96" s="26">
-        <f>Q96</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z96" s="12">
-        <f>ROUND(Y96*R96,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA96" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB96" s="11">
         <f>IFERROR(VLOOKUP(AA96,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC96" s="12">
-        <f>ROUND(Y96*AB96*R96,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD96" s="12">
-        <f>ROUND(AC96-X96,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE96" s="13">
-        <f>IFERROR(AD96/AC96,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="2:36" x14ac:dyDescent="0.25">
@@ -6173,43 +7073,53 @@
         <v>0</v>
       </c>
       <c r="S97" s="12">
-        <f>ROUND(Q97*R97,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T97" s="5">
         <v>0</v>
       </c>
       <c r="U97" s="12">
-        <f>ROUND(S97*(1-T97),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V97" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W97" s="11">
         <f>IFERROR(VLOOKUP(V97,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X97" s="12">
-        <f>ROUND(U97*W97,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y97" s="26">
-        <f>Q97</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z97" s="12">
-        <f>ROUND(Y97*R97,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA97" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB97" s="11">
         <f>IFERROR(VLOOKUP(AA97,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC97" s="12">
-        <f>ROUND(Y97*AB97*R97,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD97" s="12">
-        <f>ROUND(AC97-X97,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE97" s="13">
-        <f>IFERROR(AD97/AC97,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="2:36" x14ac:dyDescent="0.25">
@@ -6231,43 +7141,53 @@
         <v>0</v>
       </c>
       <c r="S98" s="12">
-        <f>ROUND(Q98*R98,2)</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="T98" s="5">
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f>ROUND(S98*(1-T98),2)</f>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="V98" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W98" s="11">
         <f>IFERROR(VLOOKUP(V98,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X98" s="12">
-        <f>ROUND(U98*W98,2)</f>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="Y98" s="26">
-        <f>Q98</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="Z98" s="12">
-        <f>ROUND(Y98*R98,2)</f>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AA98" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB98" s="11">
         <f>IFERROR(VLOOKUP(AA98,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC98" s="12">
-        <f>ROUND(Y98*AB98*R98,2)</f>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AD98" s="12">
-        <f>ROUND(AC98-X98,2)</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="AE98" s="13">
-        <f>IFERROR(AD98/AC98,0)</f>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
@@ -6289,43 +7209,53 @@
         <v>0</v>
       </c>
       <c r="S99" s="12">
-        <f>ROUND(Q99*R99,2)</f>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="T99" s="5">
         <v>0</v>
       </c>
       <c r="U99" s="12">
-        <f>ROUND(S99*(1-T99),2)</f>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="V99" s="25" t="s">
         <v>10</v>
       </c>
       <c r="W99" s="11">
         <f>IFERROR(VLOOKUP(V99,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="X99" s="12">
-        <f>ROUND(U99*W99,2)</f>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="Y99" s="26">
-        <f>Q99</f>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="Z99" s="12">
-        <f>ROUND(Y99*R99,2)</f>
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="AA99" s="4" t="s">
         <v>10</v>
       </c>
       <c r="AB99" s="11">
         <f>IFERROR(VLOOKUP(AA99,Curr!$B$2:$C$13,2,FALSE),0)</f>
+        <v>11.3</v>
       </c>
       <c r="AC99" s="12">
-        <f>ROUND(Y99*AB99*R99,2)</f>
+        <f t="shared" si="19"/>
+        <v>0</v>
       </c>
       <c r="AD99" s="12">
-        <f>ROUND(AC99-X99,2)</f>
+        <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="AE99" s="13">
-        <f>IFERROR(AD99/AC99,0)</f>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="2:36" x14ac:dyDescent="0.25">
@@ -6429,32 +7359,41 @@
       </c>
       <c r="Z101" s="15">
         <f>SUM(Z7:Z99)</f>
+        <v>0</v>
       </c>
       <c r="AA101" s="14"/>
       <c r="AB101" s="14"/>
       <c r="AC101" s="15">
         <f>SUM(AC7:AC99)</f>
+        <v>0</v>
       </c>
       <c r="AD101" s="15">
         <f>SUM(AD7:AD99)</f>
+        <v>0</v>
       </c>
       <c r="AE101" s="21">
-        <f>IFERROR(AD101/AC101,0)</f>
+        <f t="shared" ref="AE101" si="30">IFERROR(AD101/AC101,0)</f>
+        <v>0</v>
       </c>
       <c r="AF101" s="15">
-        <f>SUM(AF7:AF99)</f>
+        <f>SUM(AF8:AF100)</f>
+        <v>0</v>
       </c>
       <c r="AG101" s="15">
-        <f>SUM(AG7:AG99)</f>
+        <f>SUM(AG8:AG100)</f>
+        <v>0</v>
       </c>
       <c r="AH101" s="15">
-        <f>SUM(AH7:AH99)</f>
+        <f>SUM(AH8:AH100)</f>
+        <v>0</v>
       </c>
       <c r="AI101" s="15">
-        <f>SUM(AI7:AI99)</f>
+        <f>SUM(AI8:AI100)</f>
+        <v>0</v>
       </c>
       <c r="AJ101" s="15">
-        <f>SUM(AJ7:AJ99)</f>
+        <f>SUM(AJ8:AJ100)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="2:36" x14ac:dyDescent="0.25">
@@ -6504,9 +7443,7 @@
       <c r="Y103" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Z103" s="34">
-        <f>Z101</f>
-      </c>
+      <c r="Z103" s="34"/>
       <c r="AA103" s="9"/>
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
@@ -6531,8 +7468,13 @@
       <c r="V104" s="9"/>
       <c r="W104" s="9"/>
       <c r="X104" s="9"/>
-      <c r="Y104" s="34"/>
-      <c r="Z104" s="34"/>
+      <c r="Y104" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z104" s="34">
+        <f>Z103/2</f>
+        <v>0</v>
+      </c>
       <c r="AA104" s="9"/>
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
@@ -6591,6 +7533,7 @@
       </c>
       <c r="Z106" s="9">
         <f>Z103-Z107</f>
+        <v>0</v>
       </c>
       <c r="AA106" s="9"/>
       <c r="AB106" s="9"/>
@@ -6664,6 +7607,7 @@
       </c>
       <c r="Z109" s="9">
         <f>Z103*0.3</f>
+        <v>0</v>
       </c>
       <c r="AA109" s="9"/>
       <c r="AB109" s="9"/>
@@ -6685,6 +7629,7 @@
       </c>
       <c r="Z110" s="9">
         <f>Z107-Z109</f>
+        <v>0</v>
       </c>
       <c r="AA110" s="9"/>
       <c r="AB110" s="9"/>
@@ -6701,6 +7646,7 @@
       </c>
       <c r="Z111" s="9">
         <f>Z103-Z109-Z110</f>
+        <v>0</v>
       </c>
       <c r="AA111" s="9"/>
       <c r="AB111" s="9"/>
